--- a/output/version3/test/20-15/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1000</v>
+        <v>829</v>
       </c>
       <c r="C2" t="n">
-        <v>982</v>
+        <v>854</v>
       </c>
       <c r="D2" t="n">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="E2" t="n">
-        <v>846</v>
+        <v>998</v>
       </c>
       <c r="F2" t="n">
-        <v>1077</v>
+        <v>868</v>
       </c>
       <c r="G2" t="n">
-        <v>1041</v>
+        <v>924</v>
       </c>
       <c r="H2" t="n">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="I2" t="n">
-        <v>798</v>
+        <v>826</v>
       </c>
       <c r="J2" t="n">
-        <v>1009</v>
+        <v>874</v>
       </c>
       <c r="K2" t="n">
-        <v>966</v>
+        <v>1027</v>
       </c>
       <c r="L2" t="n">
-        <v>961.3</v>
+        <v>908.7</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1003</v>
+        <v>875</v>
       </c>
       <c r="C3" t="n">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="D3" t="n">
-        <v>898</v>
+        <v>1120</v>
       </c>
       <c r="E3" t="n">
-        <v>895</v>
+        <v>841</v>
       </c>
       <c r="F3" t="n">
-        <v>1068</v>
+        <v>961</v>
       </c>
       <c r="G3" t="n">
-        <v>1030</v>
+        <v>883</v>
       </c>
       <c r="H3" t="n">
-        <v>996</v>
+        <v>1009</v>
       </c>
       <c r="I3" t="n">
-        <v>1038</v>
+        <v>1071</v>
       </c>
       <c r="J3" t="n">
-        <v>916</v>
+        <v>1020</v>
       </c>
       <c r="K3" t="n">
-        <v>1022</v>
+        <v>1144</v>
       </c>
       <c r="L3" t="n">
-        <v>981.2</v>
+        <v>983.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
+        <v>1120</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D4" t="n">
+        <v>926</v>
+      </c>
+      <c r="E4" t="n">
+        <v>911</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1072</v>
+      </c>
+      <c r="G4" t="n">
         <v>996</v>
       </c>
-      <c r="C4" t="n">
-        <v>920</v>
-      </c>
-      <c r="D4" t="n">
-        <v>916</v>
-      </c>
-      <c r="E4" t="n">
-        <v>868</v>
-      </c>
-      <c r="F4" t="n">
-        <v>897</v>
-      </c>
-      <c r="G4" t="n">
-        <v>963</v>
-      </c>
       <c r="H4" t="n">
-        <v>991</v>
+        <v>1191</v>
       </c>
       <c r="I4" t="n">
-        <v>773</v>
+        <v>1065</v>
       </c>
       <c r="J4" t="n">
-        <v>1047</v>
+        <v>878</v>
       </c>
       <c r="K4" t="n">
-        <v>897</v>
+        <v>988</v>
       </c>
       <c r="L4" t="n">
-        <v>926.8</v>
+        <v>1018.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>820</v>
+      </c>
+      <c r="D5" t="n">
+        <v>898</v>
+      </c>
+      <c r="E5" t="n">
+        <v>895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>939</v>
+      </c>
+      <c r="G5" t="n">
         <v>1040</v>
       </c>
-      <c r="C5" t="n">
-        <v>942</v>
-      </c>
-      <c r="D5" t="n">
-        <v>884</v>
-      </c>
-      <c r="E5" t="n">
-        <v>864</v>
-      </c>
-      <c r="F5" t="n">
-        <v>923</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1155</v>
-      </c>
       <c r="H5" t="n">
-        <v>919</v>
+        <v>948</v>
       </c>
       <c r="I5" t="n">
-        <v>926</v>
+        <v>821</v>
       </c>
       <c r="J5" t="n">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="K5" t="n">
-        <v>856</v>
+        <v>938</v>
       </c>
       <c r="L5" t="n">
-        <v>945.1</v>
+        <v>922</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>718</v>
+        <v>795</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="E6" t="n">
-        <v>770</v>
+        <v>690</v>
       </c>
       <c r="F6" t="n">
+        <v>922</v>
+      </c>
+      <c r="G6" t="n">
+        <v>861</v>
+      </c>
+      <c r="H6" t="n">
+        <v>823</v>
+      </c>
+      <c r="I6" t="n">
         <v>881</v>
       </c>
-      <c r="G6" t="n">
-        <v>710</v>
-      </c>
-      <c r="H6" t="n">
-        <v>732</v>
-      </c>
-      <c r="I6" t="n">
-        <v>806</v>
-      </c>
       <c r="J6" t="n">
-        <v>820</v>
+        <v>733</v>
       </c>
       <c r="K6" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="L6" t="n">
-        <v>782.5</v>
+        <v>788.2</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>929</v>
+        <v>972</v>
       </c>
       <c r="C7" t="n">
-        <v>888</v>
+        <v>964</v>
       </c>
       <c r="D7" t="n">
-        <v>1060</v>
+        <v>940</v>
       </c>
       <c r="E7" t="n">
-        <v>984</v>
+        <v>928</v>
       </c>
       <c r="F7" t="n">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="G7" t="n">
-        <v>781</v>
+        <v>1024</v>
       </c>
       <c r="H7" t="n">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="I7" t="n">
-        <v>1082</v>
+        <v>927</v>
       </c>
       <c r="J7" t="n">
-        <v>857</v>
+        <v>1091</v>
       </c>
       <c r="K7" t="n">
-        <v>963</v>
+        <v>997</v>
       </c>
       <c r="L7" t="n">
-        <v>936.9</v>
+        <v>967.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>848</v>
+        <v>996</v>
       </c>
       <c r="C8" t="n">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D8" t="n">
-        <v>826</v>
+        <v>861</v>
       </c>
       <c r="E8" t="n">
-        <v>964</v>
+        <v>774</v>
       </c>
       <c r="F8" t="n">
-        <v>994</v>
+        <v>847</v>
       </c>
       <c r="G8" t="n">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="H8" t="n">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="I8" t="n">
+        <v>886</v>
+      </c>
+      <c r="J8" t="n">
         <v>881</v>
       </c>
-      <c r="J8" t="n">
-        <v>910</v>
-      </c>
       <c r="K8" t="n">
-        <v>907</v>
+        <v>1037</v>
       </c>
       <c r="L8" t="n">
-        <v>902.6</v>
+        <v>896.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>779</v>
+        <v>855</v>
       </c>
       <c r="C9" t="n">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="D9" t="n">
-        <v>934</v>
+        <v>903</v>
       </c>
       <c r="E9" t="n">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="F9" t="n">
-        <v>917</v>
+        <v>766</v>
       </c>
       <c r="G9" t="n">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="H9" t="n">
         <v>920</v>
       </c>
       <c r="I9" t="n">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="J9" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="K9" t="n">
-        <v>821</v>
+        <v>964</v>
       </c>
       <c r="L9" t="n">
-        <v>879.1</v>
+        <v>886.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>849</v>
+        <v>1044</v>
       </c>
       <c r="C10" t="n">
-        <v>850</v>
+        <v>1033</v>
       </c>
       <c r="D10" t="n">
-        <v>810</v>
+        <v>752</v>
       </c>
       <c r="E10" t="n">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="F10" t="n">
-        <v>754</v>
+        <v>783</v>
       </c>
       <c r="G10" t="n">
-        <v>1035</v>
+        <v>728</v>
       </c>
       <c r="H10" t="n">
-        <v>901</v>
+        <v>936</v>
       </c>
       <c r="I10" t="n">
-        <v>848</v>
+        <v>925</v>
       </c>
       <c r="J10" t="n">
-        <v>912</v>
+        <v>817</v>
       </c>
       <c r="K10" t="n">
-        <v>795</v>
+        <v>1028</v>
       </c>
       <c r="L10" t="n">
-        <v>866.9</v>
+        <v>897.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C11" t="n">
-        <v>974</v>
+        <v>941</v>
       </c>
       <c r="D11" t="n">
-        <v>859</v>
+        <v>894</v>
       </c>
       <c r="E11" t="n">
-        <v>1011</v>
+        <v>975</v>
       </c>
       <c r="F11" t="n">
-        <v>871</v>
+        <v>922</v>
       </c>
       <c r="G11" t="n">
-        <v>870</v>
+        <v>1022</v>
       </c>
       <c r="H11" t="n">
-        <v>1034</v>
+        <v>812</v>
       </c>
       <c r="I11" t="n">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="J11" t="n">
-        <v>1029</v>
+        <v>1010</v>
       </c>
       <c r="K11" t="n">
-        <v>945</v>
+        <v>843</v>
       </c>
       <c r="L11" t="n">
-        <v>942.4</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1096</v>
+        <v>947</v>
       </c>
       <c r="C12" t="n">
-        <v>820</v>
+        <v>976</v>
       </c>
       <c r="D12" t="n">
-        <v>1062</v>
+        <v>814</v>
       </c>
       <c r="E12" t="n">
-        <v>1001</v>
+        <v>903</v>
       </c>
       <c r="F12" t="n">
-        <v>1156</v>
+        <v>1056</v>
       </c>
       <c r="G12" t="n">
-        <v>883</v>
+        <v>997</v>
       </c>
       <c r="H12" t="n">
-        <v>799</v>
+        <v>983</v>
       </c>
       <c r="I12" t="n">
-        <v>803</v>
+        <v>894</v>
       </c>
       <c r="J12" t="n">
-        <v>1084</v>
+        <v>1035</v>
       </c>
       <c r="K12" t="n">
-        <v>1185</v>
+        <v>796</v>
       </c>
       <c r="L12" t="n">
-        <v>988.9</v>
+        <v>940.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>817</v>
+        <v>723</v>
       </c>
       <c r="C13" t="n">
-        <v>904</v>
+        <v>843</v>
       </c>
       <c r="D13" t="n">
-        <v>982</v>
+        <v>909</v>
       </c>
       <c r="E13" t="n">
-        <v>899</v>
+        <v>840</v>
       </c>
       <c r="F13" t="n">
-        <v>754</v>
+        <v>841</v>
       </c>
       <c r="G13" t="n">
-        <v>937</v>
+        <v>905</v>
       </c>
       <c r="H13" t="n">
-        <v>784</v>
+        <v>873</v>
       </c>
       <c r="I13" t="n">
-        <v>851</v>
+        <v>741</v>
       </c>
       <c r="J13" t="n">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="K13" t="n">
-        <v>788</v>
+        <v>870</v>
       </c>
       <c r="L13" t="n">
-        <v>863.4</v>
+        <v>850</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1071</v>
+        <v>1034</v>
       </c>
       <c r="C14" t="n">
-        <v>903</v>
+        <v>990</v>
       </c>
       <c r="D14" t="n">
-        <v>1011</v>
+        <v>1116</v>
       </c>
       <c r="E14" t="n">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="F14" t="n">
-        <v>808</v>
+        <v>941</v>
       </c>
       <c r="G14" t="n">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="H14" t="n">
-        <v>777</v>
+        <v>1087</v>
       </c>
       <c r="I14" t="n">
-        <v>813</v>
+        <v>1091</v>
       </c>
       <c r="J14" t="n">
-        <v>1032</v>
+        <v>966</v>
       </c>
       <c r="K14" t="n">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="L14" t="n">
-        <v>924.6</v>
+        <v>1010.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>838</v>
+        <v>928</v>
       </c>
       <c r="C15" t="n">
-        <v>966</v>
+        <v>917</v>
       </c>
       <c r="D15" t="n">
-        <v>755</v>
+        <v>1100</v>
       </c>
       <c r="E15" t="n">
+        <v>972</v>
+      </c>
+      <c r="F15" t="n">
+        <v>934</v>
+      </c>
+      <c r="G15" t="n">
+        <v>899</v>
+      </c>
+      <c r="H15" t="n">
+        <v>818</v>
+      </c>
+      <c r="I15" t="n">
         <v>1006</v>
       </c>
-      <c r="F15" t="n">
-        <v>917</v>
-      </c>
-      <c r="G15" t="n">
-        <v>992</v>
-      </c>
-      <c r="H15" t="n">
-        <v>895</v>
-      </c>
-      <c r="I15" t="n">
-        <v>964</v>
-      </c>
       <c r="J15" t="n">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="K15" t="n">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="L15" t="n">
-        <v>908.5</v>
+        <v>930.7</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>986</v>
+        <v>946</v>
       </c>
       <c r="C16" t="n">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D16" t="n">
-        <v>906</v>
+        <v>1034</v>
       </c>
       <c r="E16" t="n">
-        <v>906</v>
+        <v>1037</v>
       </c>
       <c r="F16" t="n">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="G16" t="n">
-        <v>878</v>
+        <v>1020</v>
       </c>
       <c r="H16" t="n">
-        <v>928</v>
+        <v>957</v>
       </c>
       <c r="I16" t="n">
-        <v>1016</v>
+        <v>966</v>
       </c>
       <c r="J16" t="n">
-        <v>1111</v>
+        <v>1060</v>
       </c>
       <c r="K16" t="n">
-        <v>934</v>
+        <v>1046</v>
       </c>
       <c r="L16" t="n">
-        <v>954.6</v>
+        <v>996.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>910</v>
+        <v>936</v>
       </c>
       <c r="C17" t="n">
-        <v>936</v>
+        <v>833</v>
       </c>
       <c r="D17" t="n">
-        <v>864</v>
+        <v>843</v>
       </c>
       <c r="E17" t="n">
-        <v>1146</v>
+        <v>891</v>
       </c>
       <c r="F17" t="n">
-        <v>1090</v>
+        <v>951</v>
       </c>
       <c r="G17" t="n">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="H17" t="n">
-        <v>935</v>
+        <v>998</v>
       </c>
       <c r="I17" t="n">
-        <v>1078</v>
+        <v>958</v>
       </c>
       <c r="J17" t="n">
-        <v>944</v>
+        <v>977</v>
       </c>
       <c r="K17" t="n">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="L17" t="n">
-        <v>970.1</v>
+        <v>913.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>891</v>
+        <v>866</v>
       </c>
       <c r="C18" t="n">
-        <v>822</v>
+        <v>927</v>
       </c>
       <c r="D18" t="n">
-        <v>831</v>
+        <v>925</v>
       </c>
       <c r="E18" t="n">
-        <v>836</v>
+        <v>880</v>
       </c>
       <c r="F18" t="n">
-        <v>1020</v>
+        <v>903</v>
       </c>
       <c r="G18" t="n">
-        <v>923</v>
+        <v>984</v>
       </c>
       <c r="H18" t="n">
-        <v>1065</v>
+        <v>946</v>
       </c>
       <c r="I18" t="n">
-        <v>852</v>
+        <v>1083</v>
       </c>
       <c r="J18" t="n">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="K18" t="n">
-        <v>922</v>
+        <v>1043</v>
       </c>
       <c r="L18" t="n">
-        <v>907.5</v>
+        <v>945.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>836</v>
+        <v>745</v>
       </c>
       <c r="C19" t="n">
+        <v>818</v>
+      </c>
+      <c r="D19" t="n">
+        <v>800</v>
+      </c>
+      <c r="E19" t="n">
+        <v>809</v>
+      </c>
+      <c r="F19" t="n">
+        <v>983</v>
+      </c>
+      <c r="G19" t="n">
+        <v>883</v>
+      </c>
+      <c r="H19" t="n">
+        <v>806</v>
+      </c>
+      <c r="I19" t="n">
+        <v>911</v>
+      </c>
+      <c r="J19" t="n">
+        <v>984</v>
+      </c>
+      <c r="K19" t="n">
         <v>879</v>
       </c>
-      <c r="D19" t="n">
-        <v>739</v>
-      </c>
-      <c r="E19" t="n">
-        <v>831</v>
-      </c>
-      <c r="F19" t="n">
-        <v>837</v>
-      </c>
-      <c r="G19" t="n">
-        <v>833</v>
-      </c>
-      <c r="H19" t="n">
-        <v>820</v>
-      </c>
-      <c r="I19" t="n">
-        <v>986</v>
-      </c>
-      <c r="J19" t="n">
-        <v>858</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1116</v>
-      </c>
       <c r="L19" t="n">
-        <v>873.5</v>
+        <v>861.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>852</v>
+        <v>959</v>
       </c>
       <c r="C20" t="n">
-        <v>939</v>
+        <v>980</v>
       </c>
       <c r="D20" t="n">
-        <v>920</v>
+        <v>886</v>
       </c>
       <c r="E20" t="n">
-        <v>957</v>
+        <v>891</v>
       </c>
       <c r="F20" t="n">
-        <v>1081</v>
+        <v>893</v>
       </c>
       <c r="G20" t="n">
-        <v>877</v>
+        <v>1014</v>
       </c>
       <c r="H20" t="n">
-        <v>835</v>
+        <v>985</v>
       </c>
       <c r="I20" t="n">
-        <v>1033</v>
+        <v>1134</v>
       </c>
       <c r="J20" t="n">
-        <v>1086</v>
+        <v>1028</v>
       </c>
       <c r="K20" t="n">
-        <v>1010</v>
+        <v>944</v>
       </c>
       <c r="L20" t="n">
-        <v>959</v>
+        <v>971.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>814</v>
+        <v>953</v>
       </c>
       <c r="C21" t="n">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="D21" t="n">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E21" t="n">
-        <v>781</v>
+        <v>1020</v>
       </c>
       <c r="F21" t="n">
-        <v>1031</v>
+        <v>835</v>
       </c>
       <c r="G21" t="n">
-        <v>980</v>
+        <v>1061</v>
       </c>
       <c r="H21" t="n">
-        <v>1048</v>
+        <v>859</v>
       </c>
       <c r="I21" t="n">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="J21" t="n">
-        <v>929</v>
+        <v>822</v>
       </c>
       <c r="K21" t="n">
-        <v>1036</v>
+        <v>1156</v>
       </c>
       <c r="L21" t="n">
-        <v>932.5</v>
+        <v>943.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="C22" t="n">
-        <v>982</v>
+        <v>899</v>
       </c>
       <c r="D22" t="n">
-        <v>824</v>
+        <v>946</v>
       </c>
       <c r="E22" t="n">
-        <v>777</v>
+        <v>835</v>
       </c>
       <c r="F22" t="n">
-        <v>942</v>
+        <v>853</v>
       </c>
       <c r="G22" t="n">
-        <v>940</v>
+        <v>800</v>
       </c>
       <c r="H22" t="n">
-        <v>1044</v>
+        <v>807</v>
       </c>
       <c r="I22" t="n">
-        <v>1060</v>
+        <v>820</v>
       </c>
       <c r="J22" t="n">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="K22" t="n">
-        <v>844</v>
+        <v>885</v>
       </c>
       <c r="L22" t="n">
-        <v>914</v>
+        <v>861.5</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="C23" t="n">
         <v>1080</v>
       </c>
       <c r="D23" t="n">
-        <v>1060</v>
+        <v>1219</v>
       </c>
       <c r="E23" t="n">
-        <v>1147</v>
+        <v>1111</v>
       </c>
       <c r="F23" t="n">
-        <v>1043</v>
+        <v>1159</v>
       </c>
       <c r="G23" t="n">
-        <v>1008</v>
+        <v>1078</v>
       </c>
       <c r="H23" t="n">
-        <v>1096</v>
+        <v>956</v>
       </c>
       <c r="I23" t="n">
-        <v>1272</v>
+        <v>1108</v>
       </c>
       <c r="J23" t="n">
-        <v>1108</v>
+        <v>1158</v>
       </c>
       <c r="K23" t="n">
-        <v>892</v>
+        <v>981</v>
       </c>
       <c r="L23" t="n">
-        <v>1063.1</v>
+        <v>1079.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="C24" t="n">
-        <v>993</v>
+        <v>979</v>
       </c>
       <c r="D24" t="n">
-        <v>1051</v>
+        <v>928</v>
       </c>
       <c r="E24" t="n">
-        <v>1189</v>
+        <v>1109</v>
       </c>
       <c r="F24" t="n">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="G24" t="n">
-        <v>1057</v>
+        <v>860</v>
       </c>
       <c r="H24" t="n">
-        <v>1089</v>
+        <v>1064</v>
       </c>
       <c r="I24" t="n">
-        <v>960</v>
+        <v>1012</v>
       </c>
       <c r="J24" t="n">
-        <v>917</v>
+        <v>841</v>
       </c>
       <c r="K24" t="n">
-        <v>795</v>
+        <v>846</v>
       </c>
       <c r="L24" t="n">
-        <v>1012.2</v>
+        <v>974</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>894</v>
+        <v>1033</v>
       </c>
       <c r="C25" t="n">
-        <v>1107</v>
+        <v>906</v>
       </c>
       <c r="D25" t="n">
-        <v>852</v>
+        <v>934</v>
       </c>
       <c r="E25" t="n">
-        <v>909</v>
+        <v>1034</v>
       </c>
       <c r="F25" t="n">
-        <v>858</v>
+        <v>969</v>
       </c>
       <c r="G25" t="n">
-        <v>1078</v>
+        <v>813</v>
       </c>
       <c r="H25" t="n">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="I25" t="n">
-        <v>980</v>
+        <v>834</v>
       </c>
       <c r="J25" t="n">
-        <v>890</v>
+        <v>1049</v>
       </c>
       <c r="K25" t="n">
-        <v>984</v>
+        <v>1040</v>
       </c>
       <c r="L25" t="n">
-        <v>946.8</v>
+        <v>954.3</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>974</v>
+        <v>849</v>
       </c>
       <c r="C26" t="n">
-        <v>943</v>
+        <v>1077</v>
       </c>
       <c r="D26" t="n">
-        <v>783</v>
+        <v>814</v>
       </c>
       <c r="E26" t="n">
-        <v>1072</v>
+        <v>939</v>
       </c>
       <c r="F26" t="n">
-        <v>857</v>
+        <v>812</v>
       </c>
       <c r="G26" t="n">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="H26" t="n">
-        <v>817</v>
+        <v>712</v>
       </c>
       <c r="I26" t="n">
-        <v>858</v>
+        <v>789</v>
       </c>
       <c r="J26" t="n">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="K26" t="n">
-        <v>848</v>
+        <v>1075</v>
       </c>
       <c r="L26" t="n">
-        <v>875.8</v>
+        <v>863.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1121</v>
+        <v>879</v>
       </c>
       <c r="C27" t="n">
-        <v>1162</v>
+        <v>1110</v>
       </c>
       <c r="D27" t="n">
-        <v>985</v>
+        <v>1047</v>
       </c>
       <c r="E27" t="n">
-        <v>961</v>
+        <v>1019</v>
       </c>
       <c r="F27" t="n">
-        <v>1042</v>
+        <v>1069</v>
       </c>
       <c r="G27" t="n">
-        <v>1017</v>
+        <v>1094</v>
       </c>
       <c r="H27" t="n">
-        <v>926</v>
+        <v>1050</v>
       </c>
       <c r="I27" t="n">
-        <v>952</v>
+        <v>1204</v>
       </c>
       <c r="J27" t="n">
-        <v>1038</v>
+        <v>862</v>
       </c>
       <c r="K27" t="n">
-        <v>857</v>
+        <v>1025</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.1</v>
+        <v>1035.9</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1057</v>
+        <v>872</v>
       </c>
       <c r="C28" t="n">
+        <v>899</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E28" t="n">
+        <v>930</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G28" t="n">
+        <v>957</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1164</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1116</v>
+      </c>
+      <c r="J28" t="n">
         <v>937</v>
       </c>
-      <c r="D28" t="n">
-        <v>1044</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1040</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1052</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1027</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1110</v>
-      </c>
-      <c r="J28" t="n">
-        <v>900</v>
-      </c>
       <c r="K28" t="n">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="L28" t="n">
-        <v>1024.4</v>
+        <v>1010.4</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>872</v>
+        <v>978</v>
       </c>
       <c r="C29" t="n">
-        <v>853</v>
+        <v>1024</v>
       </c>
       <c r="D29" t="n">
-        <v>1005</v>
+        <v>1039</v>
       </c>
       <c r="E29" t="n">
-        <v>957</v>
+        <v>892</v>
       </c>
       <c r="F29" t="n">
-        <v>1030</v>
+        <v>974</v>
       </c>
       <c r="G29" t="n">
-        <v>949</v>
+        <v>892</v>
       </c>
       <c r="H29" t="n">
-        <v>945</v>
+        <v>1011</v>
       </c>
       <c r="I29" t="n">
-        <v>882</v>
+        <v>948</v>
       </c>
       <c r="J29" t="n">
-        <v>786</v>
+        <v>998</v>
       </c>
       <c r="K29" t="n">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="L29" t="n">
-        <v>940.9</v>
+        <v>987.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="C30" t="n">
-        <v>906</v>
+        <v>1003</v>
       </c>
       <c r="D30" t="n">
-        <v>867</v>
+        <v>958</v>
       </c>
       <c r="E30" t="n">
-        <v>872</v>
+        <v>907</v>
       </c>
       <c r="F30" t="n">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="G30" t="n">
-        <v>814</v>
+        <v>1050</v>
       </c>
       <c r="H30" t="n">
-        <v>1026</v>
+        <v>846</v>
       </c>
       <c r="I30" t="n">
-        <v>862</v>
+        <v>1084</v>
       </c>
       <c r="J30" t="n">
-        <v>1030</v>
+        <v>947</v>
       </c>
       <c r="K30" t="n">
-        <v>888</v>
+        <v>1020</v>
       </c>
       <c r="L30" t="n">
-        <v>907.5</v>
+        <v>962.9</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1129</v>
+        <v>1049</v>
       </c>
       <c r="C31" t="n">
-        <v>818</v>
+        <v>1016</v>
       </c>
       <c r="D31" t="n">
-        <v>905</v>
+        <v>787</v>
       </c>
       <c r="E31" t="n">
-        <v>830</v>
+        <v>927</v>
       </c>
       <c r="F31" t="n">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="G31" t="n">
-        <v>891</v>
+        <v>809</v>
       </c>
       <c r="H31" t="n">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="I31" t="n">
-        <v>1018</v>
+        <v>804</v>
       </c>
       <c r="J31" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="K31" t="n">
-        <v>808</v>
+        <v>917</v>
       </c>
       <c r="L31" t="n">
-        <v>920.9</v>
+        <v>912.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1090</v>
+        <v>866</v>
       </c>
       <c r="C32" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D32" t="n">
+        <v>837</v>
+      </c>
+      <c r="E32" t="n">
+        <v>860</v>
+      </c>
+      <c r="F32" t="n">
         <v>923</v>
       </c>
-      <c r="D32" t="n">
-        <v>1044</v>
-      </c>
-      <c r="E32" t="n">
-        <v>771</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1064</v>
-      </c>
       <c r="G32" t="n">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="H32" t="n">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="I32" t="n">
-        <v>874</v>
+        <v>937</v>
       </c>
       <c r="J32" t="n">
-        <v>1048</v>
+        <v>843</v>
       </c>
       <c r="K32" t="n">
-        <v>1148</v>
+        <v>1006</v>
       </c>
       <c r="L32" t="n">
-        <v>964</v>
+        <v>910.2</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>854</v>
+        <v>1110</v>
       </c>
       <c r="C33" t="n">
-        <v>1025</v>
+        <v>1058</v>
       </c>
       <c r="D33" t="n">
-        <v>788</v>
+        <v>930</v>
       </c>
       <c r="E33" t="n">
-        <v>948</v>
+        <v>1042</v>
       </c>
       <c r="F33" t="n">
-        <v>1041</v>
+        <v>1114</v>
       </c>
       <c r="G33" t="n">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="H33" t="n">
-        <v>919</v>
+        <v>936</v>
       </c>
       <c r="I33" t="n">
-        <v>863</v>
+        <v>947</v>
       </c>
       <c r="J33" t="n">
-        <v>961</v>
+        <v>898</v>
       </c>
       <c r="K33" t="n">
-        <v>1066</v>
+        <v>894</v>
       </c>
       <c r="L33" t="n">
-        <v>928.2</v>
+        <v>979.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>897</v>
+        <v>914</v>
       </c>
       <c r="C34" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D34" t="n">
+        <v>862</v>
+      </c>
+      <c r="E34" t="n">
+        <v>985</v>
+      </c>
+      <c r="F34" t="n">
+        <v>910</v>
+      </c>
+      <c r="G34" t="n">
         <v>893</v>
       </c>
-      <c r="D34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>976</v>
-      </c>
-      <c r="F34" t="n">
-        <v>871</v>
-      </c>
-      <c r="G34" t="n">
-        <v>812</v>
-      </c>
       <c r="H34" t="n">
-        <v>744</v>
+        <v>861</v>
       </c>
       <c r="I34" t="n">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="J34" t="n">
-        <v>774</v>
+        <v>731</v>
       </c>
       <c r="K34" t="n">
-        <v>764</v>
+        <v>967</v>
       </c>
       <c r="L34" t="n">
-        <v>856.5</v>
+        <v>898</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>813</v>
+        <v>1072</v>
       </c>
       <c r="C35" t="n">
-        <v>859</v>
+        <v>899</v>
       </c>
       <c r="D35" t="n">
-        <v>934</v>
+        <v>873</v>
       </c>
       <c r="E35" t="n">
-        <v>941</v>
+        <v>760</v>
       </c>
       <c r="F35" t="n">
-        <v>731</v>
+        <v>1012</v>
       </c>
       <c r="G35" t="n">
+        <v>857</v>
+      </c>
+      <c r="H35" t="n">
+        <v>844</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1032</v>
+      </c>
+      <c r="J35" t="n">
+        <v>816</v>
+      </c>
+      <c r="K35" t="n">
         <v>820</v>
       </c>
-      <c r="H35" t="n">
-        <v>945</v>
-      </c>
-      <c r="I35" t="n">
-        <v>745</v>
-      </c>
-      <c r="J35" t="n">
-        <v>957</v>
-      </c>
-      <c r="K35" t="n">
-        <v>780</v>
-      </c>
       <c r="L35" t="n">
-        <v>852.5</v>
+        <v>898.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1204</v>
+        <v>1052</v>
       </c>
       <c r="C36" t="n">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="D36" t="n">
-        <v>1155</v>
+        <v>1083</v>
       </c>
       <c r="E36" t="n">
-        <v>1034</v>
+        <v>1225</v>
       </c>
       <c r="F36" t="n">
-        <v>1096</v>
+        <v>1015</v>
       </c>
       <c r="G36" t="n">
-        <v>1090</v>
+        <v>992</v>
       </c>
       <c r="H36" t="n">
-        <v>1156</v>
+        <v>1078</v>
       </c>
       <c r="I36" t="n">
-        <v>963</v>
+        <v>1025</v>
       </c>
       <c r="J36" t="n">
-        <v>964</v>
+        <v>1059</v>
       </c>
       <c r="K36" t="n">
-        <v>1025</v>
+        <v>1217</v>
       </c>
       <c r="L36" t="n">
-        <v>1067</v>
+        <v>1074.3</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>880</v>
+        <v>927</v>
       </c>
       <c r="C37" t="n">
-        <v>850</v>
+        <v>910</v>
       </c>
       <c r="D37" t="n">
-        <v>957</v>
+        <v>769</v>
       </c>
       <c r="E37" t="n">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="F37" t="n">
-        <v>933</v>
+        <v>804</v>
       </c>
       <c r="G37" t="n">
-        <v>880</v>
+        <v>818</v>
       </c>
       <c r="H37" t="n">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="I37" t="n">
-        <v>960</v>
+        <v>853</v>
       </c>
       <c r="J37" t="n">
-        <v>888</v>
+        <v>761</v>
       </c>
       <c r="K37" t="n">
-        <v>849</v>
+        <v>815</v>
       </c>
       <c r="L37" t="n">
-        <v>892</v>
+        <v>840.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>930</v>
+        <v>877</v>
       </c>
       <c r="C38" t="n">
-        <v>850</v>
+        <v>912</v>
       </c>
       <c r="D38" t="n">
-        <v>987</v>
+        <v>831</v>
       </c>
       <c r="E38" t="n">
-        <v>1085</v>
+        <v>842</v>
       </c>
       <c r="F38" t="n">
-        <v>1063</v>
+        <v>971</v>
       </c>
       <c r="G38" t="n">
-        <v>820</v>
+        <v>928</v>
       </c>
       <c r="H38" t="n">
-        <v>875</v>
+        <v>961</v>
       </c>
       <c r="I38" t="n">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="J38" t="n">
-        <v>828</v>
+        <v>883</v>
       </c>
       <c r="K38" t="n">
-        <v>925</v>
+        <v>837</v>
       </c>
       <c r="L38" t="n">
-        <v>921.6</v>
+        <v>890.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="C39" t="n">
-        <v>780</v>
+        <v>887</v>
       </c>
       <c r="D39" t="n">
+        <v>770</v>
+      </c>
+      <c r="E39" t="n">
         <v>849</v>
       </c>
-      <c r="E39" t="n">
-        <v>772</v>
-      </c>
       <c r="F39" t="n">
-        <v>834</v>
+        <v>766</v>
       </c>
       <c r="G39" t="n">
-        <v>816</v>
+        <v>763</v>
       </c>
       <c r="H39" t="n">
-        <v>825</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="n">
-        <v>924</v>
+        <v>865</v>
       </c>
       <c r="J39" t="n">
-        <v>786</v>
+        <v>887</v>
       </c>
       <c r="K39" t="n">
-        <v>852</v>
+        <v>1067</v>
       </c>
       <c r="L39" t="n">
-        <v>828.8</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>875</v>
+        <v>1021</v>
       </c>
       <c r="C40" t="n">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="D40" t="n">
-        <v>834</v>
+        <v>857</v>
       </c>
       <c r="E40" t="n">
-        <v>1028</v>
+        <v>859</v>
       </c>
       <c r="F40" t="n">
-        <v>872</v>
+        <v>843</v>
       </c>
       <c r="G40" t="n">
-        <v>828</v>
+        <v>798</v>
       </c>
       <c r="H40" t="n">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="I40" t="n">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="J40" t="n">
-        <v>956</v>
+        <v>829</v>
       </c>
       <c r="K40" t="n">
-        <v>839</v>
+        <v>882</v>
       </c>
       <c r="L40" t="n">
-        <v>890.6</v>
+        <v>878.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>850</v>
+      </c>
+      <c r="C41" t="n">
+        <v>834</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E41" t="n">
+        <v>829</v>
+      </c>
+      <c r="F41" t="n">
+        <v>830</v>
+      </c>
+      <c r="G41" t="n">
+        <v>979</v>
+      </c>
+      <c r="H41" t="n">
         <v>949</v>
       </c>
-      <c r="C41" t="n">
-        <v>921</v>
-      </c>
-      <c r="D41" t="n">
-        <v>940</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1069</v>
-      </c>
-      <c r="F41" t="n">
-        <v>841</v>
-      </c>
-      <c r="G41" t="n">
-        <v>918</v>
-      </c>
-      <c r="H41" t="n">
-        <v>847</v>
-      </c>
       <c r="I41" t="n">
-        <v>1002</v>
+        <v>810</v>
       </c>
       <c r="J41" t="n">
-        <v>951</v>
+        <v>1074</v>
       </c>
       <c r="K41" t="n">
-        <v>918</v>
+        <v>934</v>
       </c>
       <c r="L41" t="n">
-        <v>935.6</v>
+        <v>919</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>792</v>
+        <v>745</v>
       </c>
       <c r="C42" t="n">
-        <v>791</v>
+        <v>942</v>
       </c>
       <c r="D42" t="n">
-        <v>1014</v>
+        <v>976</v>
       </c>
       <c r="E42" t="n">
-        <v>919</v>
+        <v>845</v>
       </c>
       <c r="F42" t="n">
-        <v>1051</v>
+        <v>724</v>
       </c>
       <c r="G42" t="n">
-        <v>886</v>
+        <v>1206</v>
       </c>
       <c r="H42" t="n">
-        <v>968</v>
+        <v>766</v>
       </c>
       <c r="I42" t="n">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J42" t="n">
-        <v>901</v>
+        <v>971</v>
       </c>
       <c r="K42" t="n">
-        <v>955</v>
+        <v>872</v>
       </c>
       <c r="L42" t="n">
-        <v>912.6</v>
+        <v>889.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
+        <v>738</v>
+      </c>
+      <c r="C43" t="n">
+        <v>883</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E43" t="n">
         <v>1008</v>
       </c>
-      <c r="C43" t="n">
-        <v>927</v>
-      </c>
-      <c r="D43" t="n">
-        <v>877</v>
-      </c>
-      <c r="E43" t="n">
-        <v>783</v>
-      </c>
       <c r="F43" t="n">
-        <v>811</v>
+        <v>918</v>
       </c>
       <c r="G43" t="n">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="H43" t="n">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="I43" t="n">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="J43" t="n">
-        <v>1047</v>
+        <v>790</v>
       </c>
       <c r="K43" t="n">
-        <v>791</v>
+        <v>937</v>
       </c>
       <c r="L43" t="n">
-        <v>865.2</v>
+        <v>865.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>926</v>
+        <v>952</v>
       </c>
       <c r="C44" t="n">
-        <v>973</v>
+        <v>831</v>
       </c>
       <c r="D44" t="n">
-        <v>777</v>
+        <v>967</v>
       </c>
       <c r="E44" t="n">
-        <v>1031</v>
+        <v>866</v>
       </c>
       <c r="F44" t="n">
-        <v>1038</v>
+        <v>847</v>
       </c>
       <c r="G44" t="n">
-        <v>875</v>
+        <v>936</v>
       </c>
       <c r="H44" t="n">
-        <v>879</v>
+        <v>814</v>
       </c>
       <c r="I44" t="n">
-        <v>965</v>
+        <v>911</v>
       </c>
       <c r="J44" t="n">
-        <v>1084</v>
+        <v>895</v>
       </c>
       <c r="K44" t="n">
-        <v>949</v>
+        <v>861</v>
       </c>
       <c r="L44" t="n">
-        <v>949.7</v>
+        <v>888</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>874</v>
+        <v>1002</v>
       </c>
       <c r="C45" t="n">
-        <v>1147</v>
+        <v>1048</v>
       </c>
       <c r="D45" t="n">
-        <v>997</v>
+        <v>850</v>
       </c>
       <c r="E45" t="n">
-        <v>855</v>
+        <v>946</v>
       </c>
       <c r="F45" t="n">
-        <v>846</v>
+        <v>916</v>
       </c>
       <c r="G45" t="n">
-        <v>858</v>
+        <v>996</v>
       </c>
       <c r="H45" t="n">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="I45" t="n">
-        <v>912</v>
+        <v>1046</v>
       </c>
       <c r="J45" t="n">
-        <v>886</v>
+        <v>931</v>
       </c>
       <c r="K45" t="n">
-        <v>986</v>
+        <v>1096</v>
       </c>
       <c r="L45" t="n">
-        <v>937.2</v>
+        <v>983.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1001</v>
+        <v>936</v>
       </c>
       <c r="C46" t="n">
-        <v>1144</v>
+        <v>905</v>
       </c>
       <c r="D46" t="n">
-        <v>916</v>
+        <v>935</v>
       </c>
       <c r="E46" t="n">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="F46" t="n">
-        <v>1068</v>
+        <v>895</v>
       </c>
       <c r="G46" t="n">
-        <v>1036</v>
+        <v>1051</v>
       </c>
       <c r="H46" t="n">
-        <v>879</v>
+        <v>927</v>
       </c>
       <c r="I46" t="n">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="J46" t="n">
-        <v>944</v>
+        <v>900</v>
       </c>
       <c r="K46" t="n">
-        <v>957</v>
+        <v>1063</v>
       </c>
       <c r="L46" t="n">
-        <v>964</v>
+        <v>930.1</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="C47" t="n">
-        <v>937</v>
+        <v>998</v>
       </c>
       <c r="D47" t="n">
-        <v>954</v>
+        <v>1153</v>
       </c>
       <c r="E47" t="n">
-        <v>775</v>
+        <v>1081</v>
       </c>
       <c r="F47" t="n">
-        <v>869</v>
+        <v>1110</v>
       </c>
       <c r="G47" t="n">
-        <v>984</v>
+        <v>964</v>
       </c>
       <c r="H47" t="n">
-        <v>926</v>
+        <v>1138</v>
       </c>
       <c r="I47" t="n">
-        <v>998</v>
+        <v>1094</v>
       </c>
       <c r="J47" t="n">
-        <v>972</v>
+        <v>1050</v>
       </c>
       <c r="K47" t="n">
-        <v>1042</v>
+        <v>996</v>
       </c>
       <c r="L47" t="n">
-        <v>947.1</v>
+        <v>1058.5</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1047</v>
+        <v>942</v>
       </c>
       <c r="C48" t="n">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="D48" t="n">
-        <v>998</v>
+        <v>1101</v>
       </c>
       <c r="E48" t="n">
-        <v>972</v>
+        <v>882</v>
       </c>
       <c r="F48" t="n">
-        <v>846</v>
+        <v>935</v>
       </c>
       <c r="G48" t="n">
-        <v>858</v>
+        <v>804</v>
       </c>
       <c r="H48" t="n">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="I48" t="n">
-        <v>887</v>
+        <v>967</v>
       </c>
       <c r="J48" t="n">
-        <v>870</v>
+        <v>981</v>
       </c>
       <c r="K48" t="n">
-        <v>1078</v>
+        <v>803</v>
       </c>
       <c r="L48" t="n">
-        <v>923.7</v>
+        <v>907.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C49" t="n">
-        <v>924</v>
+        <v>1062</v>
       </c>
       <c r="D49" t="n">
-        <v>939</v>
+        <v>889</v>
       </c>
       <c r="E49" t="n">
-        <v>979</v>
+        <v>920</v>
       </c>
       <c r="F49" t="n">
-        <v>967</v>
+        <v>883</v>
       </c>
       <c r="G49" t="n">
-        <v>957</v>
+        <v>891</v>
       </c>
       <c r="H49" t="n">
-        <v>1101</v>
+        <v>868</v>
       </c>
       <c r="I49" t="n">
-        <v>1009</v>
+        <v>1035</v>
       </c>
       <c r="J49" t="n">
-        <v>1016</v>
+        <v>973</v>
       </c>
       <c r="K49" t="n">
-        <v>835</v>
+        <v>955</v>
       </c>
       <c r="L49" t="n">
-        <v>972.8</v>
+        <v>947.5</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1090</v>
+        <v>1052</v>
       </c>
       <c r="C50" t="n">
-        <v>1084</v>
+        <v>965</v>
       </c>
       <c r="D50" t="n">
-        <v>922</v>
+        <v>885</v>
       </c>
       <c r="E50" t="n">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="F50" t="n">
-        <v>1075</v>
+        <v>896</v>
       </c>
       <c r="G50" t="n">
-        <v>875</v>
+        <v>817</v>
       </c>
       <c r="H50" t="n">
-        <v>912</v>
+        <v>1011</v>
       </c>
       <c r="I50" t="n">
-        <v>911</v>
+        <v>998</v>
       </c>
       <c r="J50" t="n">
-        <v>858</v>
+        <v>895</v>
       </c>
       <c r="K50" t="n">
-        <v>1003</v>
+        <v>899</v>
       </c>
       <c r="L50" t="n">
-        <v>959.6</v>
+        <v>928.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="C51" t="n">
-        <v>933</v>
+        <v>962</v>
       </c>
       <c r="D51" t="n">
+        <v>991</v>
+      </c>
+      <c r="E51" t="n">
+        <v>803</v>
+      </c>
+      <c r="F51" t="n">
+        <v>959</v>
+      </c>
+      <c r="G51" t="n">
+        <v>924</v>
+      </c>
+      <c r="H51" t="n">
+        <v>897</v>
+      </c>
+      <c r="I51" t="n">
         <v>922</v>
       </c>
-      <c r="E51" t="n">
-        <v>863</v>
-      </c>
-      <c r="F51" t="n">
-        <v>971</v>
-      </c>
-      <c r="G51" t="n">
-        <v>964</v>
-      </c>
-      <c r="H51" t="n">
-        <v>909</v>
-      </c>
-      <c r="I51" t="n">
-        <v>898</v>
-      </c>
       <c r="J51" t="n">
-        <v>786</v>
+        <v>1064</v>
       </c>
       <c r="K51" t="n">
-        <v>983</v>
+        <v>853</v>
       </c>
       <c r="L51" t="n">
-        <v>915.9</v>
+        <v>927.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>941.12</v>
+        <v>928.6799999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>928.76</v>
+        <v>943.98</v>
       </c>
       <c r="D52" t="n">
-        <v>920.28</v>
+        <v>935.2</v>
       </c>
       <c r="E52" t="n">
-        <v>930.34</v>
+        <v>920.12</v>
       </c>
       <c r="F52" t="n">
-        <v>953.5</v>
+        <v>930</v>
       </c>
       <c r="G52" t="n">
-        <v>916.54</v>
+        <v>922.72</v>
       </c>
       <c r="H52" t="n">
-        <v>920.84</v>
+        <v>928.38</v>
       </c>
       <c r="I52" t="n">
-        <v>925.2</v>
+        <v>945.3</v>
       </c>
       <c r="J52" t="n">
-        <v>938.1799999999999</v>
+        <v>928.28</v>
       </c>
       <c r="K52" t="n">
-        <v>925.98</v>
+        <v>954.52</v>
       </c>
       <c r="L52" t="n">
-        <v>930.074</v>
+        <v>933.7180000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.738211154937744</v>
+        <v>6.657070398330688</v>
       </c>
       <c r="C2" t="n">
-        <v>9.970136404037476</v>
+        <v>7.107380151748657</v>
       </c>
       <c r="D2" t="n">
-        <v>7.436384439468384</v>
+        <v>8.90080189704895</v>
       </c>
       <c r="E2" t="n">
-        <v>7.798380613327026</v>
+        <v>9.494301319122314</v>
       </c>
       <c r="F2" t="n">
-        <v>9.891460657119751</v>
+        <v>6.778272390365601</v>
       </c>
       <c r="G2" t="n">
-        <v>9.246001243591309</v>
+        <v>7.314862251281738</v>
       </c>
       <c r="H2" t="n">
-        <v>9.637851476669312</v>
+        <v>8.084896326065063</v>
       </c>
       <c r="I2" t="n">
-        <v>6.355037450790405</v>
+        <v>6.580256938934326</v>
       </c>
       <c r="J2" t="n">
-        <v>8.671941757202148</v>
+        <v>8.559711933135986</v>
       </c>
       <c r="K2" t="n">
-        <v>7.721394300460815</v>
+        <v>9.964603424072266</v>
       </c>
       <c r="L2" t="n">
-        <v>8.646679949760436</v>
+        <v>7.944215703010559</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.526957035064697</v>
+        <v>7.099436521530151</v>
       </c>
       <c r="C3" t="n">
-        <v>6.745457172393799</v>
+        <v>7.747763872146606</v>
       </c>
       <c r="D3" t="n">
-        <v>6.87614107131958</v>
+        <v>9.808991670608521</v>
       </c>
       <c r="E3" t="n">
-        <v>6.814281463623047</v>
+        <v>6.756819725036621</v>
       </c>
       <c r="F3" t="n">
-        <v>8.677637100219727</v>
+        <v>7.278436183929443</v>
       </c>
       <c r="G3" t="n">
-        <v>7.176247358322144</v>
+        <v>7.228591203689575</v>
       </c>
       <c r="H3" t="n">
-        <v>7.000178813934326</v>
+        <v>9.175605773925781</v>
       </c>
       <c r="I3" t="n">
-        <v>7.327862501144409</v>
+        <v>8.711297035217285</v>
       </c>
       <c r="J3" t="n">
-        <v>6.42563533782959</v>
+        <v>7.979149580001831</v>
       </c>
       <c r="K3" t="n">
-        <v>6.840094804763794</v>
+        <v>9.460384368896484</v>
       </c>
       <c r="L3" t="n">
-        <v>7.141049265861511</v>
+        <v>8.12464759349823</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.714834690093994</v>
+        <v>9.220474243164062</v>
       </c>
       <c r="C4" t="n">
-        <v>6.245107173919678</v>
+        <v>9.220501184463501</v>
       </c>
       <c r="D4" t="n">
-        <v>6.598186016082764</v>
+        <v>9.02602481842041</v>
       </c>
       <c r="E4" t="n">
-        <v>6.224127531051636</v>
+        <v>6.820621490478516</v>
       </c>
       <c r="F4" t="n">
-        <v>7.435067653656006</v>
+        <v>8.837563037872314</v>
       </c>
       <c r="G4" t="n">
-        <v>7.502413988113403</v>
+        <v>7.635547399520874</v>
       </c>
       <c r="H4" t="n">
-        <v>8.00464129447937</v>
+        <v>9.804025411605835</v>
       </c>
       <c r="I4" t="n">
-        <v>6.248084783554077</v>
+        <v>9.724732398986816</v>
       </c>
       <c r="J4" t="n">
-        <v>8.863449573516846</v>
+        <v>6.955945730209351</v>
       </c>
       <c r="K4" t="n">
-        <v>6.233622789382935</v>
+        <v>9.400017976760864</v>
       </c>
       <c r="L4" t="n">
-        <v>7.106953549385071</v>
+        <v>8.664545369148254</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>8.063442707061768</v>
+        <v>8.123381376266479</v>
       </c>
       <c r="C5" t="n">
-        <v>6.053132295608521</v>
+        <v>6.298109769821167</v>
       </c>
       <c r="D5" t="n">
-        <v>6.095480442047119</v>
+        <v>7.053629875183105</v>
       </c>
       <c r="E5" t="n">
-        <v>6.140365123748779</v>
+        <v>6.249125719070435</v>
       </c>
       <c r="F5" t="n">
-        <v>5.800211191177368</v>
+        <v>9.463431835174561</v>
       </c>
       <c r="G5" t="n">
-        <v>8.322286128997803</v>
+        <v>8.778151988983154</v>
       </c>
       <c r="H5" t="n">
-        <v>5.955326795578003</v>
+        <v>7.886397838592529</v>
       </c>
       <c r="I5" t="n">
-        <v>6.171276807785034</v>
+        <v>7.061529636383057</v>
       </c>
       <c r="J5" t="n">
-        <v>7.609082698822021</v>
+        <v>6.05953311920166</v>
       </c>
       <c r="K5" t="n">
-        <v>5.782294273376465</v>
+        <v>8.703308582305908</v>
       </c>
       <c r="L5" t="n">
-        <v>6.599289846420288</v>
+        <v>7.567659974098206</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.493393898010254</v>
+        <v>6.191230058670044</v>
       </c>
       <c r="C6" t="n">
-        <v>5.719000101089478</v>
+        <v>5.910471200942993</v>
       </c>
       <c r="D6" t="n">
-        <v>5.435042142868042</v>
+        <v>6.127878427505493</v>
       </c>
       <c r="E6" t="n">
-        <v>5.82115626335144</v>
+        <v>5.833139657974243</v>
       </c>
       <c r="F6" t="n">
-        <v>5.70995831489563</v>
+        <v>8.391589164733887</v>
       </c>
       <c r="G6" t="n">
-        <v>5.515450954437256</v>
+        <v>6.524882555007935</v>
       </c>
       <c r="H6" t="n">
-        <v>5.228200674057007</v>
+        <v>5.709967613220215</v>
       </c>
       <c r="I6" t="n">
-        <v>5.486024141311646</v>
+        <v>8.0699462890625</v>
       </c>
       <c r="J6" t="n">
-        <v>5.846925735473633</v>
+        <v>6.104438781738281</v>
       </c>
       <c r="K6" t="n">
-        <v>5.582971572875977</v>
+        <v>6.122466087341309</v>
       </c>
       <c r="L6" t="n">
-        <v>5.783812379837036</v>
+        <v>6.49860098361969</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.192683458328247</v>
+        <v>7.588398218154907</v>
       </c>
       <c r="C7" t="n">
-        <v>6.923053026199341</v>
+        <v>8.260559797286987</v>
       </c>
       <c r="D7" t="n">
-        <v>9.61653470993042</v>
+        <v>7.63811993598938</v>
       </c>
       <c r="E7" t="n">
-        <v>8.689342021942139</v>
+        <v>8.747799396514893</v>
       </c>
       <c r="F7" t="n">
-        <v>8.147734642028809</v>
+        <v>10.34356594085693</v>
       </c>
       <c r="G7" t="n">
-        <v>6.695439577102661</v>
+        <v>9.613946437835693</v>
       </c>
       <c r="H7" t="n">
-        <v>6.894983053207397</v>
+        <v>7.392263412475586</v>
       </c>
       <c r="I7" t="n">
-        <v>9.213512420654297</v>
+        <v>8.859471797943115</v>
       </c>
       <c r="J7" t="n">
-        <v>7.21467661857605</v>
+        <v>9.109777450561523</v>
       </c>
       <c r="K7" t="n">
-        <v>8.623448133468628</v>
+        <v>9.000053405761719</v>
       </c>
       <c r="L7" t="n">
-        <v>8.021140766143798</v>
+        <v>8.655395579338073</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>6.496605634689331</v>
+        <v>10.13481307029724</v>
       </c>
       <c r="C8" t="n">
-        <v>6.555475950241089</v>
+        <v>8.317471265792847</v>
       </c>
       <c r="D8" t="n">
-        <v>6.270199060440063</v>
+        <v>6.990679740905762</v>
       </c>
       <c r="E8" t="n">
-        <v>7.961796522140503</v>
+        <v>6.957295417785645</v>
       </c>
       <c r="F8" t="n">
-        <v>9.156712532043457</v>
+        <v>7.367392539978027</v>
       </c>
       <c r="G8" t="n">
-        <v>7.584306001663208</v>
+        <v>7.421075582504272</v>
       </c>
       <c r="H8" t="n">
-        <v>6.531525850296021</v>
+        <v>7.357271432876587</v>
       </c>
       <c r="I8" t="n">
-        <v>8.280014514923096</v>
+        <v>7.566202878952026</v>
       </c>
       <c r="J8" t="n">
-        <v>8.761353731155396</v>
+        <v>7.678959131240845</v>
       </c>
       <c r="K8" t="n">
-        <v>7.086114406585693</v>
+        <v>9.5611252784729</v>
       </c>
       <c r="L8" t="n">
-        <v>7.468410420417785</v>
+        <v>7.935228633880615</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>6.90156364440918</v>
+        <v>7.432049512863159</v>
       </c>
       <c r="C9" t="n">
-        <v>7.740856885910034</v>
+        <v>8.310329675674438</v>
       </c>
       <c r="D9" t="n">
-        <v>6.459202766418457</v>
+        <v>7.317860126495361</v>
       </c>
       <c r="E9" t="n">
-        <v>6.568425893783569</v>
+        <v>7.402105331420898</v>
       </c>
       <c r="F9" t="n">
-        <v>6.89258337020874</v>
+        <v>7.122354984283447</v>
       </c>
       <c r="G9" t="n">
-        <v>6.785367250442505</v>
+        <v>7.041043996810913</v>
       </c>
       <c r="H9" t="n">
-        <v>7.966784954071045</v>
+        <v>7.499409914016724</v>
       </c>
       <c r="I9" t="n">
-        <v>7.958311080932617</v>
+        <v>8.820515394210815</v>
       </c>
       <c r="J9" t="n">
-        <v>6.660674095153809</v>
+        <v>7.886892795562744</v>
       </c>
       <c r="K9" t="n">
-        <v>6.990824937820435</v>
+        <v>9.19956374168396</v>
       </c>
       <c r="L9" t="n">
-        <v>7.092459487915039</v>
+        <v>7.803212547302246</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.806297540664673</v>
+        <v>8.465895175933838</v>
       </c>
       <c r="C10" t="n">
-        <v>7.344434022903442</v>
+        <v>9.418038129806519</v>
       </c>
       <c r="D10" t="n">
-        <v>5.949564218521118</v>
+        <v>6.434601306915283</v>
       </c>
       <c r="E10" t="n">
-        <v>6.35197639465332</v>
+        <v>8.573171377182007</v>
       </c>
       <c r="F10" t="n">
-        <v>6.820268869400024</v>
+        <v>6.220172166824341</v>
       </c>
       <c r="G10" t="n">
-        <v>8.456985473632812</v>
+        <v>6.565754890441895</v>
       </c>
       <c r="H10" t="n">
-        <v>5.887197971343994</v>
+        <v>8.184137105941772</v>
       </c>
       <c r="I10" t="n">
-        <v>5.950534820556641</v>
+        <v>6.819620609283447</v>
       </c>
       <c r="J10" t="n">
-        <v>8.48692774772644</v>
+        <v>6.523891448974609</v>
       </c>
       <c r="K10" t="n">
-        <v>6.377439260482788</v>
+        <v>9.139244794845581</v>
       </c>
       <c r="L10" t="n">
-        <v>6.843162631988525</v>
+        <v>7.634452700614929</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.436257600784302</v>
+        <v>6.751289367675781</v>
       </c>
       <c r="C11" t="n">
-        <v>7.354497194290161</v>
+        <v>7.277471542358398</v>
       </c>
       <c r="D11" t="n">
-        <v>6.764301776885986</v>
+        <v>7.186222076416016</v>
       </c>
       <c r="E11" t="n">
-        <v>6.822631597518921</v>
+        <v>9.007047414779663</v>
       </c>
       <c r="F11" t="n">
-        <v>6.85653281211853</v>
+        <v>7.043068647384644</v>
       </c>
       <c r="G11" t="n">
-        <v>6.969257354736328</v>
+        <v>9.346529245376587</v>
       </c>
       <c r="H11" t="n">
-        <v>7.893396615982056</v>
+        <v>7.303404092788696</v>
       </c>
       <c r="I11" t="n">
-        <v>6.816646099090576</v>
+        <v>6.957281112670898</v>
       </c>
       <c r="J11" t="n">
-        <v>8.493587970733643</v>
+        <v>6.946792840957642</v>
       </c>
       <c r="K11" t="n">
-        <v>9.030003547668457</v>
+        <v>7.359289884567261</v>
       </c>
       <c r="L11" t="n">
-        <v>7.343711256980896</v>
+        <v>7.517839622497559</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>9.625940561294556</v>
+        <v>9.403038740158081</v>
       </c>
       <c r="C12" t="n">
-        <v>6.680628538131714</v>
+        <v>10.38079357147217</v>
       </c>
       <c r="D12" t="n">
-        <v>10.46034550666809</v>
+        <v>7.218202114105225</v>
       </c>
       <c r="E12" t="n">
-        <v>8.361741065979004</v>
+        <v>7.731367826461792</v>
       </c>
       <c r="F12" t="n">
-        <v>10.57948088645935</v>
+        <v>8.911282062530518</v>
       </c>
       <c r="G12" t="n">
-        <v>7.032696485519409</v>
+        <v>7.938406467437744</v>
       </c>
       <c r="H12" t="n">
-        <v>7.107020139694214</v>
+        <v>10.43185615539551</v>
       </c>
       <c r="I12" t="n">
-        <v>7.048674821853638</v>
+        <v>7.613190889358521</v>
       </c>
       <c r="J12" t="n">
-        <v>12.34028005599976</v>
+        <v>10.06976771354675</v>
       </c>
       <c r="K12" t="n">
-        <v>11.94942402839661</v>
+        <v>8.461060047149658</v>
       </c>
       <c r="L12" t="n">
-        <v>9.118623208999633</v>
+        <v>8.815896558761597</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.829383611679077</v>
+        <v>6.688252449035645</v>
       </c>
       <c r="C13" t="n">
-        <v>7.212257623672485</v>
+        <v>6.9682776927948</v>
       </c>
       <c r="D13" t="n">
-        <v>7.569841146469116</v>
+        <v>7.88491678237915</v>
       </c>
       <c r="E13" t="n">
-        <v>6.832241535186768</v>
+        <v>7.609108686447144</v>
       </c>
       <c r="F13" t="n">
-        <v>6.910556793212891</v>
+        <v>6.805654048919678</v>
       </c>
       <c r="G13" t="n">
-        <v>6.085693120956421</v>
+        <v>6.860031366348267</v>
       </c>
       <c r="H13" t="n">
-        <v>5.975486993789673</v>
+        <v>6.321390867233276</v>
       </c>
       <c r="I13" t="n">
-        <v>6.260755777359009</v>
+        <v>6.565895080566406</v>
       </c>
       <c r="J13" t="n">
-        <v>6.925501108169556</v>
+        <v>9.059441328048706</v>
       </c>
       <c r="K13" t="n">
-        <v>5.561531782150269</v>
+        <v>7.670469999313354</v>
       </c>
       <c r="L13" t="n">
-        <v>6.516324949264527</v>
+        <v>7.243343830108643</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>9.526699304580688</v>
+        <v>9.73766565322876</v>
       </c>
       <c r="C14" t="n">
-        <v>8.322839260101318</v>
+        <v>9.222513437271118</v>
       </c>
       <c r="D14" t="n">
-        <v>6.94543719291687</v>
+        <v>8.557219266891479</v>
       </c>
       <c r="E14" t="n">
-        <v>8.657821416854858</v>
+        <v>9.105301380157471</v>
       </c>
       <c r="F14" t="n">
-        <v>6.961905002593994</v>
+        <v>7.96722412109375</v>
       </c>
       <c r="G14" t="n">
-        <v>6.397365808486938</v>
+        <v>8.779807806015015</v>
       </c>
       <c r="H14" t="n">
-        <v>6.564462184906006</v>
+        <v>10.54273104667664</v>
       </c>
       <c r="I14" t="n">
-        <v>6.920501708984375</v>
+        <v>9.849883317947388</v>
       </c>
       <c r="J14" t="n">
-        <v>7.762809276580811</v>
+        <v>7.947671413421631</v>
       </c>
       <c r="K14" t="n">
-        <v>7.465596914291382</v>
+        <v>7.712869644165039</v>
       </c>
       <c r="L14" t="n">
-        <v>7.552543807029724</v>
+        <v>8.942288708686828</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>6.269197702407837</v>
+        <v>6.79966926574707</v>
       </c>
       <c r="C15" t="n">
-        <v>7.652137041091919</v>
+        <v>7.583188056945801</v>
       </c>
       <c r="D15" t="n">
-        <v>6.745002269744873</v>
+        <v>8.669415235519409</v>
       </c>
       <c r="E15" t="n">
-        <v>7.800710439682007</v>
+        <v>7.448041439056396</v>
       </c>
       <c r="F15" t="n">
-        <v>6.492639541625977</v>
+        <v>8.781617164611816</v>
       </c>
       <c r="G15" t="n">
-        <v>8.163252353668213</v>
+        <v>8.577715635299683</v>
       </c>
       <c r="H15" t="n">
-        <v>6.555964469909668</v>
+        <v>7.711181402206421</v>
       </c>
       <c r="I15" t="n">
-        <v>7.955838918685913</v>
+        <v>7.589334726333618</v>
       </c>
       <c r="J15" t="n">
-        <v>6.561931848526001</v>
+        <v>7.132269144058228</v>
       </c>
       <c r="K15" t="n">
-        <v>6.880111217498779</v>
+        <v>6.779746770858765</v>
       </c>
       <c r="L15" t="n">
-        <v>7.107678580284118</v>
+        <v>7.707217884063721</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.392870187759399</v>
+        <v>7.250511884689331</v>
       </c>
       <c r="C16" t="n">
-        <v>6.692599773406982</v>
+        <v>8.040006875991821</v>
       </c>
       <c r="D16" t="n">
-        <v>6.560949563980103</v>
+        <v>8.889344930648804</v>
       </c>
       <c r="E16" t="n">
-        <v>6.669629096984863</v>
+        <v>8.700352191925049</v>
       </c>
       <c r="F16" t="n">
-        <v>6.513572454452515</v>
+        <v>7.693873882293701</v>
       </c>
       <c r="G16" t="n">
-        <v>6.585860013961792</v>
+        <v>9.25640606880188</v>
       </c>
       <c r="H16" t="n">
-        <v>6.625777244567871</v>
+        <v>7.120364427566528</v>
       </c>
       <c r="I16" t="n">
-        <v>7.661566972732544</v>
+        <v>7.523361206054688</v>
       </c>
       <c r="J16" t="n">
-        <v>8.524343013763428</v>
+        <v>9.143703699111938</v>
       </c>
       <c r="K16" t="n">
-        <v>6.725015878677368</v>
+        <v>8.845441102981567</v>
       </c>
       <c r="L16" t="n">
-        <v>6.995218420028687</v>
+        <v>8.246336627006531</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>6.848720788955688</v>
+        <v>8.400596380233765</v>
       </c>
       <c r="C17" t="n">
-        <v>8.195198535919189</v>
+        <v>7.397179126739502</v>
       </c>
       <c r="D17" t="n">
-        <v>7.215345621109009</v>
+        <v>8.728264331817627</v>
       </c>
       <c r="E17" t="n">
-        <v>8.790143013000488</v>
+        <v>7.822065353393555</v>
       </c>
       <c r="F17" t="n">
-        <v>7.955817937850952</v>
+        <v>8.496859073638916</v>
       </c>
       <c r="G17" t="n">
-        <v>6.768411874771118</v>
+        <v>8.548711776733398</v>
       </c>
       <c r="H17" t="n">
-        <v>6.837240219116211</v>
+        <v>9.962115049362183</v>
       </c>
       <c r="I17" t="n">
-        <v>9.884769678115845</v>
+        <v>7.891400575637817</v>
       </c>
       <c r="J17" t="n">
-        <v>6.676616907119751</v>
+        <v>9.366641283035278</v>
       </c>
       <c r="K17" t="n">
-        <v>6.989859104156494</v>
+        <v>7.517337799072266</v>
       </c>
       <c r="L17" t="n">
-        <v>7.616212368011475</v>
+        <v>8.413117074966431</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>5.947547197341919</v>
+        <v>6.85451865196228</v>
       </c>
       <c r="C18" t="n">
-        <v>6.02931809425354</v>
+        <v>7.666979551315308</v>
       </c>
       <c r="D18" t="n">
-        <v>6.60749077796936</v>
+        <v>7.972182750701904</v>
       </c>
       <c r="E18" t="n">
-        <v>6.452516078948975</v>
+        <v>6.937898397445679</v>
       </c>
       <c r="F18" t="n">
-        <v>8.003283500671387</v>
+        <v>6.627096652984619</v>
       </c>
       <c r="G18" t="n">
-        <v>7.553621768951416</v>
+        <v>7.396157741546631</v>
       </c>
       <c r="H18" t="n">
-        <v>8.554253101348877</v>
+        <v>7.438387870788574</v>
       </c>
       <c r="I18" t="n">
-        <v>6.291005849838257</v>
+        <v>9.658094167709351</v>
       </c>
       <c r="J18" t="n">
-        <v>7.721880435943604</v>
+        <v>6.804664850234985</v>
       </c>
       <c r="K18" t="n">
-        <v>7.672993421554565</v>
+        <v>8.466396331787109</v>
       </c>
       <c r="L18" t="n">
-        <v>7.08339102268219</v>
+        <v>7.582237696647644</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.224176168441772</v>
+        <v>6.685982942581177</v>
       </c>
       <c r="C19" t="n">
-        <v>6.800760746002197</v>
+        <v>6.341847658157349</v>
       </c>
       <c r="D19" t="n">
-        <v>6.286531448364258</v>
+        <v>6.524859189987183</v>
       </c>
       <c r="E19" t="n">
-        <v>6.576782464981079</v>
+        <v>7.092959403991699</v>
       </c>
       <c r="F19" t="n">
-        <v>7.014184713363647</v>
+        <v>8.517844676971436</v>
       </c>
       <c r="G19" t="n">
-        <v>7.257062911987305</v>
+        <v>7.432576894760132</v>
       </c>
       <c r="H19" t="n">
-        <v>6.023672819137573</v>
+        <v>6.51587986946106</v>
       </c>
       <c r="I19" t="n">
-        <v>8.905830860137939</v>
+        <v>8.094393968582153</v>
       </c>
       <c r="J19" t="n">
-        <v>6.872504949569702</v>
+        <v>8.598074674606323</v>
       </c>
       <c r="K19" t="n">
-        <v>8.808620691299438</v>
+        <v>7.894476652145386</v>
       </c>
       <c r="L19" t="n">
-        <v>7.077012777328491</v>
+        <v>7.369889593124389</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.180744886398315</v>
+        <v>8.809561967849731</v>
       </c>
       <c r="C20" t="n">
-        <v>7.209670543670654</v>
+        <v>8.206128358840942</v>
       </c>
       <c r="D20" t="n">
-        <v>7.327873229980469</v>
+        <v>7.714863061904907</v>
       </c>
       <c r="E20" t="n">
-        <v>6.592256784439087</v>
+        <v>7.128334999084473</v>
       </c>
       <c r="F20" t="n">
-        <v>8.468455076217651</v>
+        <v>7.142328977584839</v>
       </c>
       <c r="G20" t="n">
-        <v>7.429175138473511</v>
+        <v>8.870544195175171</v>
       </c>
       <c r="H20" t="n">
-        <v>7.522355079650879</v>
+        <v>10.47380423545837</v>
       </c>
       <c r="I20" t="n">
-        <v>8.845507621765137</v>
+        <v>9.945649147033691</v>
       </c>
       <c r="J20" t="n">
-        <v>8.898860454559326</v>
+        <v>9.979117631912231</v>
       </c>
       <c r="K20" t="n">
-        <v>8.516918182373047</v>
+        <v>9.167398452758789</v>
       </c>
       <c r="L20" t="n">
-        <v>7.799181699752808</v>
+        <v>8.743773102760315</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>6.901979207992554</v>
+        <v>8.910516977310181</v>
       </c>
       <c r="C21" t="n">
-        <v>7.137327432632446</v>
+        <v>7.071197032928467</v>
       </c>
       <c r="D21" t="n">
-        <v>7.121444463729858</v>
+        <v>7.87842583656311</v>
       </c>
       <c r="E21" t="n">
-        <v>6.718427896499634</v>
+        <v>9.586047649383545</v>
       </c>
       <c r="F21" t="n">
-        <v>8.415612936019897</v>
+        <v>7.195701360702515</v>
       </c>
       <c r="G21" t="n">
-        <v>8.039170026779175</v>
+        <v>8.164206266403198</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300831317901611</v>
+        <v>7.344816207885742</v>
       </c>
       <c r="I21" t="n">
-        <v>7.175375699996948</v>
+        <v>8.025529861450195</v>
       </c>
       <c r="J21" t="n">
-        <v>7.623183488845825</v>
+        <v>7.310857057571411</v>
       </c>
       <c r="K21" t="n">
-        <v>9.036088466644287</v>
+        <v>8.524771928787231</v>
       </c>
       <c r="L21" t="n">
-        <v>7.746944093704224</v>
+        <v>8.00120701789856</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.368936538696289</v>
+        <v>6.128882646560669</v>
       </c>
       <c r="C22" t="n">
-        <v>6.327046632766724</v>
+        <v>6.317413091659546</v>
       </c>
       <c r="D22" t="n">
-        <v>6.066747903823853</v>
+        <v>8.230055570602417</v>
       </c>
       <c r="E22" t="n">
-        <v>6.064256906509399</v>
+        <v>6.773235559463501</v>
       </c>
       <c r="F22" t="n">
-        <v>5.8128981590271</v>
+        <v>6.787707567214966</v>
       </c>
       <c r="G22" t="n">
-        <v>6.865683794021606</v>
+        <v>6.421659708023071</v>
       </c>
       <c r="H22" t="n">
-        <v>7.791752099990845</v>
+        <v>6.392705202102661</v>
       </c>
       <c r="I22" t="n">
-        <v>7.828582763671875</v>
+        <v>6.632202625274658</v>
       </c>
       <c r="J22" t="n">
-        <v>6.049616575241089</v>
+        <v>6.338720321655273</v>
       </c>
       <c r="K22" t="n">
-        <v>6.444628238677979</v>
+        <v>6.424799680709839</v>
       </c>
       <c r="L22" t="n">
-        <v>6.562014961242676</v>
+        <v>6.64473819732666</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>7.529352188110352</v>
+        <v>7.796705007553101</v>
       </c>
       <c r="C23" t="n">
-        <v>9.052489042282104</v>
+        <v>9.800781726837158</v>
       </c>
       <c r="D23" t="n">
-        <v>9.22261118888855</v>
+        <v>9.847184419631958</v>
       </c>
       <c r="E23" t="n">
-        <v>10.26989006996155</v>
+        <v>9.144192218780518</v>
       </c>
       <c r="F23" t="n">
-        <v>7.182747364044189</v>
+        <v>10.36013078689575</v>
       </c>
       <c r="G23" t="n">
-        <v>9.074909448623657</v>
+        <v>9.881580829620361</v>
       </c>
       <c r="H23" t="n">
-        <v>9.912316560745239</v>
+        <v>7.780696392059326</v>
       </c>
       <c r="I23" t="n">
-        <v>8.554232835769653</v>
+        <v>9.154682159423828</v>
       </c>
       <c r="J23" t="n">
-        <v>10.37610769271851</v>
+        <v>8.06951379776001</v>
       </c>
       <c r="K23" t="n">
-        <v>7.152293682098389</v>
+        <v>9.140167951583862</v>
       </c>
       <c r="L23" t="n">
-        <v>8.832695007324219</v>
+        <v>9.097563529014588</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>8.468471765518188</v>
+        <v>7.528398036956787</v>
       </c>
       <c r="C24" t="n">
-        <v>7.809131860733032</v>
+        <v>8.558724641799927</v>
       </c>
       <c r="D24" t="n">
-        <v>8.974154233932495</v>
+        <v>7.956218242645264</v>
       </c>
       <c r="E24" t="n">
-        <v>11.45735740661621</v>
+        <v>9.837432384490967</v>
       </c>
       <c r="F24" t="n">
-        <v>9.311332225799561</v>
+        <v>9.579072952270508</v>
       </c>
       <c r="G24" t="n">
-        <v>13.96909856796265</v>
+        <v>7.812106370925903</v>
       </c>
       <c r="H24" t="n">
-        <v>11.33336591720581</v>
+        <v>9.664899587631226</v>
       </c>
       <c r="I24" t="n">
-        <v>8.249547481536865</v>
+        <v>9.516721725463867</v>
       </c>
       <c r="J24" t="n">
-        <v>7.767773866653442</v>
+        <v>7.579658031463623</v>
       </c>
       <c r="K24" t="n">
-        <v>7.495965480804443</v>
+        <v>7.34977126121521</v>
       </c>
       <c r="L24" t="n">
-        <v>9.483619880676269</v>
+        <v>8.538300323486329</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>7.106977462768555</v>
+        <v>8.562662601470947</v>
       </c>
       <c r="C25" t="n">
-        <v>9.520734071731567</v>
+        <v>7.023112058639526</v>
       </c>
       <c r="D25" t="n">
-        <v>7.685997486114502</v>
+        <v>7.868470907211304</v>
       </c>
       <c r="E25" t="n">
-        <v>7.935365915298462</v>
+        <v>6.721381902694702</v>
       </c>
       <c r="F25" t="n">
-        <v>7.360326766967773</v>
+        <v>8.288846969604492</v>
       </c>
       <c r="G25" t="n">
-        <v>8.932233095169067</v>
+        <v>7.079481363296509</v>
       </c>
       <c r="H25" t="n">
-        <v>7.608176231384277</v>
+        <v>7.440023422241211</v>
       </c>
       <c r="I25" t="n">
-        <v>7.493980884552002</v>
+        <v>7.219607591629028</v>
       </c>
       <c r="J25" t="n">
-        <v>7.047674655914307</v>
+        <v>9.336719512939453</v>
       </c>
       <c r="K25" t="n">
-        <v>7.353333711624146</v>
+        <v>9.244922637939453</v>
       </c>
       <c r="L25" t="n">
-        <v>7.804480028152466</v>
+        <v>7.878522896766663</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.070373296737671</v>
+        <v>7.494425058364868</v>
       </c>
       <c r="C26" t="n">
-        <v>6.941928386688232</v>
+        <v>10.00800466537476</v>
       </c>
       <c r="D26" t="n">
-        <v>6.903010606765747</v>
+        <v>6.768004894256592</v>
       </c>
       <c r="E26" t="n">
-        <v>9.539170980453491</v>
+        <v>8.697897434234619</v>
       </c>
       <c r="F26" t="n">
-        <v>7.956329345703125</v>
+        <v>6.75490665435791</v>
       </c>
       <c r="G26" t="n">
-        <v>7.171317577362061</v>
+        <v>6.631098031997681</v>
       </c>
       <c r="H26" t="n">
-        <v>6.794712543487549</v>
+        <v>6.549315929412842</v>
       </c>
       <c r="I26" t="n">
-        <v>7.999709844589233</v>
+        <v>6.915885210037231</v>
       </c>
       <c r="J26" t="n">
-        <v>9.705068588256836</v>
+        <v>6.917889595031738</v>
       </c>
       <c r="K26" t="n">
-        <v>7.357415199279785</v>
+        <v>10.94060897827148</v>
       </c>
       <c r="L26" t="n">
-        <v>7.943903636932373</v>
+        <v>7.767803645133972</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.85831618309021</v>
+        <v>7.525327205657959</v>
       </c>
       <c r="C27" t="n">
-        <v>10.86795377731323</v>
+        <v>9.164162874221802</v>
       </c>
       <c r="D27" t="n">
-        <v>9.221666812896729</v>
+        <v>9.716479778289795</v>
       </c>
       <c r="E27" t="n">
-        <v>8.365720510482788</v>
+        <v>9.331208229064941</v>
       </c>
       <c r="F27" t="n">
-        <v>7.605168581008911</v>
+        <v>8.401161432266235</v>
       </c>
       <c r="G27" t="n">
-        <v>9.124323606491089</v>
+        <v>9.425525665283203</v>
       </c>
       <c r="H27" t="n">
-        <v>7.265681505203247</v>
+        <v>9.804490566253662</v>
       </c>
       <c r="I27" t="n">
-        <v>7.377224206924438</v>
+        <v>11.01233696937561</v>
       </c>
       <c r="J27" t="n">
-        <v>9.020524263381958</v>
+        <v>7.602272510528564</v>
       </c>
       <c r="K27" t="n">
-        <v>6.687117099761963</v>
+        <v>9.073383808135986</v>
       </c>
       <c r="L27" t="n">
-        <v>8.639369654655457</v>
+        <v>9.105634903907776</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>8.687842607498169</v>
+        <v>7.813650846481323</v>
       </c>
       <c r="C28" t="n">
-        <v>7.160315752029419</v>
+        <v>8.009475946426392</v>
       </c>
       <c r="D28" t="n">
-        <v>8.992043495178223</v>
+        <v>9.561676979064941</v>
       </c>
       <c r="E28" t="n">
-        <v>9.466896295547485</v>
+        <v>8.764171838760376</v>
       </c>
       <c r="F28" t="n">
-        <v>9.97155237197876</v>
+        <v>8.958641767501831</v>
       </c>
       <c r="G28" t="n">
-        <v>9.442588090896606</v>
+        <v>7.827569484710693</v>
       </c>
       <c r="H28" t="n">
-        <v>9.89454174041748</v>
+        <v>9.677346467971802</v>
       </c>
       <c r="I28" t="n">
-        <v>9.712498426437378</v>
+        <v>8.326290369033813</v>
       </c>
       <c r="J28" t="n">
-        <v>7.525998592376709</v>
+        <v>7.936300039291382</v>
       </c>
       <c r="K28" t="n">
-        <v>9.586333751678467</v>
+        <v>9.14374303817749</v>
       </c>
       <c r="L28" t="n">
-        <v>9.04406111240387</v>
+        <v>8.601886677742005</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>8.870456218719482</v>
+        <v>10.01647329330444</v>
       </c>
       <c r="C29" t="n">
-        <v>7.286556005477905</v>
+        <v>10.40353775024414</v>
       </c>
       <c r="D29" t="n">
-        <v>9.744993686676025</v>
+        <v>10.89922976493835</v>
       </c>
       <c r="E29" t="n">
-        <v>9.178657531738281</v>
+        <v>8.355709075927734</v>
       </c>
       <c r="F29" t="n">
-        <v>9.462378740310669</v>
+        <v>8.285897493362427</v>
       </c>
       <c r="G29" t="n">
-        <v>10.01201295852661</v>
+        <v>8.118832349777222</v>
       </c>
       <c r="H29" t="n">
-        <v>9.056459665298462</v>
+        <v>9.668837785720825</v>
       </c>
       <c r="I29" t="n">
-        <v>6.739882230758667</v>
+        <v>8.546705961227417</v>
       </c>
       <c r="J29" t="n">
-        <v>7.39770770072937</v>
+        <v>8.543700933456421</v>
       </c>
       <c r="K29" t="n">
-        <v>10.7388641834259</v>
+        <v>10.29629158973694</v>
       </c>
       <c r="L29" t="n">
-        <v>8.848796892166138</v>
+        <v>9.313521599769592</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.0550696849823</v>
+        <v>8.439982414245605</v>
       </c>
       <c r="C30" t="n">
-        <v>7.104414701461792</v>
+        <v>8.168677091598511</v>
       </c>
       <c r="D30" t="n">
-        <v>7.287974119186401</v>
+        <v>8.522174835205078</v>
       </c>
       <c r="E30" t="n">
-        <v>7.161880731582642</v>
+        <v>7.259124994277954</v>
       </c>
       <c r="F30" t="n">
-        <v>7.964790344238281</v>
+        <v>7.648492336273193</v>
       </c>
       <c r="G30" t="n">
-        <v>7.525431632995605</v>
+        <v>9.991538047790527</v>
       </c>
       <c r="H30" t="n">
-        <v>9.866912126541138</v>
+        <v>7.279456853866577</v>
       </c>
       <c r="I30" t="n">
-        <v>7.461021184921265</v>
+        <v>9.645421981811523</v>
       </c>
       <c r="J30" t="n">
-        <v>8.047028064727783</v>
+        <v>9.132237911224365</v>
       </c>
       <c r="K30" t="n">
-        <v>7.035735607147217</v>
+        <v>8.861362457275391</v>
       </c>
       <c r="L30" t="n">
-        <v>7.651025819778442</v>
+        <v>8.494846892356872</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>10.10978674888611</v>
+        <v>10.20450019836426</v>
       </c>
       <c r="C31" t="n">
-        <v>7.810192346572876</v>
+        <v>9.214016199111938</v>
       </c>
       <c r="D31" t="n">
-        <v>6.318461656570435</v>
+        <v>6.690088272094727</v>
       </c>
       <c r="E31" t="n">
-        <v>7.107410192489624</v>
+        <v>8.777648448944092</v>
       </c>
       <c r="F31" t="n">
-        <v>8.455487966537476</v>
+        <v>8.706842660903931</v>
       </c>
       <c r="G31" t="n">
-        <v>7.003151416778564</v>
+        <v>7.442637205123901</v>
       </c>
       <c r="H31" t="n">
-        <v>6.933852434158325</v>
+        <v>8.93575119972229</v>
       </c>
       <c r="I31" t="n">
-        <v>9.258954286575317</v>
+        <v>7.150888204574585</v>
       </c>
       <c r="J31" t="n">
-        <v>9.148277282714844</v>
+        <v>8.477438688278198</v>
       </c>
       <c r="K31" t="n">
-        <v>7.895999908447266</v>
+        <v>8.590136051177979</v>
       </c>
       <c r="L31" t="n">
-        <v>8.004157423973083</v>
+        <v>8.418994712829591</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.60537624359131</v>
+        <v>7.358729124069214</v>
       </c>
       <c r="C32" t="n">
-        <v>8.19514536857605</v>
+        <v>10.64084386825562</v>
       </c>
       <c r="D32" t="n">
-        <v>10.19506287574768</v>
+        <v>7.13533091545105</v>
       </c>
       <c r="E32" t="n">
-        <v>6.353320598602295</v>
+        <v>7.37222695350647</v>
       </c>
       <c r="F32" t="n">
-        <v>8.782646179199219</v>
+        <v>7.085467100143433</v>
       </c>
       <c r="G32" t="n">
-        <v>7.00024151802063</v>
+        <v>7.083948373794556</v>
       </c>
       <c r="H32" t="n">
-        <v>6.896463871002197</v>
+        <v>6.767389535903931</v>
       </c>
       <c r="I32" t="n">
-        <v>6.522884368896484</v>
+        <v>8.044455766677856</v>
       </c>
       <c r="J32" t="n">
-        <v>8.867949247360229</v>
+        <v>6.271506309509277</v>
       </c>
       <c r="K32" t="n">
-        <v>8.572668552398682</v>
+        <v>10.10772800445557</v>
       </c>
       <c r="L32" t="n">
-        <v>8.199175882339478</v>
+        <v>7.786762595176697</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>6.548849821090698</v>
+        <v>10.32722091674805</v>
       </c>
       <c r="C33" t="n">
-        <v>9.10030722618103</v>
+        <v>9.021985530853271</v>
       </c>
       <c r="D33" t="n">
-        <v>6.682013511657715</v>
+        <v>8.039506196975708</v>
       </c>
       <c r="E33" t="n">
-        <v>7.918360948562622</v>
+        <v>10.02144432067871</v>
       </c>
       <c r="F33" t="n">
-        <v>9.147705078125</v>
+        <v>9.066909074783325</v>
       </c>
       <c r="G33" t="n">
-        <v>7.007165193557739</v>
+        <v>7.508356332778931</v>
       </c>
       <c r="H33" t="n">
-        <v>8.317315578460693</v>
+        <v>6.990241050720215</v>
       </c>
       <c r="I33" t="n">
-        <v>7.157284736633301</v>
+        <v>8.069987058639526</v>
       </c>
       <c r="J33" t="n">
-        <v>8.747228145599365</v>
+        <v>7.275443077087402</v>
       </c>
       <c r="K33" t="n">
-        <v>10.00855374336243</v>
+        <v>7.743755102157593</v>
       </c>
       <c r="L33" t="n">
-        <v>8.06347839832306</v>
+        <v>8.406484866142273</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.200146675109863</v>
+        <v>7.690429210662842</v>
       </c>
       <c r="C34" t="n">
-        <v>8.000110149383545</v>
+        <v>8.541259050369263</v>
       </c>
       <c r="D34" t="n">
-        <v>9.096900701522827</v>
+        <v>8.219100713729858</v>
       </c>
       <c r="E34" t="n">
-        <v>8.047556638717651</v>
+        <v>8.930725336074829</v>
       </c>
       <c r="F34" t="n">
-        <v>7.25917911529541</v>
+        <v>7.144272327423096</v>
       </c>
       <c r="G34" t="n">
-        <v>5.925565958023071</v>
+        <v>8.559725761413574</v>
       </c>
       <c r="H34" t="n">
-        <v>6.122934103012085</v>
+        <v>7.784160137176514</v>
       </c>
       <c r="I34" t="n">
-        <v>6.425681114196777</v>
+        <v>8.063982963562012</v>
       </c>
       <c r="J34" t="n">
-        <v>6.860126256942749</v>
+        <v>6.233102321624756</v>
       </c>
       <c r="K34" t="n">
-        <v>6.618201971054077</v>
+        <v>25.23487067222595</v>
       </c>
       <c r="L34" t="n">
-        <v>7.255640268325806</v>
+        <v>9.64016284942627</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.681015253067017</v>
+        <v>9.516323566436768</v>
       </c>
       <c r="C35" t="n">
-        <v>8.303439378738403</v>
+        <v>7.879942655563354</v>
       </c>
       <c r="D35" t="n">
-        <v>9.287949800491333</v>
+        <v>8.08690881729126</v>
       </c>
       <c r="E35" t="n">
-        <v>9.465540409088135</v>
+        <v>7.939266443252563</v>
       </c>
       <c r="F35" t="n">
-        <v>7.635181427001953</v>
+        <v>10.24088907241821</v>
       </c>
       <c r="G35" t="n">
-        <v>7.898998498916626</v>
+        <v>8.163212299346924</v>
       </c>
       <c r="H35" t="n">
-        <v>8.545329332351685</v>
+        <v>7.739771842956543</v>
       </c>
       <c r="I35" t="n">
-        <v>6.83844518661499</v>
+        <v>9.351670980453491</v>
       </c>
       <c r="J35" t="n">
-        <v>8.561244249343872</v>
+        <v>7.685915231704712</v>
       </c>
       <c r="K35" t="n">
-        <v>6.956916093826294</v>
+        <v>7.909352779388428</v>
       </c>
       <c r="L35" t="n">
-        <v>8.11740596294403</v>
+        <v>8.451325368881225</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>10.78481674194336</v>
+        <v>10.75956130027771</v>
       </c>
       <c r="C36" t="n">
-        <v>9.665562868118286</v>
+        <v>10.27083921432495</v>
       </c>
       <c r="D36" t="n">
-        <v>9.564671754837036</v>
+        <v>9.419986009597778</v>
       </c>
       <c r="E36" t="n">
-        <v>8.657008409500122</v>
+        <v>10.18703651428223</v>
       </c>
       <c r="F36" t="n">
-        <v>10.86437129974365</v>
+        <v>8.883475542068481</v>
       </c>
       <c r="G36" t="n">
-        <v>9.536381959915161</v>
+        <v>9.559686422348022</v>
       </c>
       <c r="H36" t="n">
-        <v>10.27387475967407</v>
+        <v>8.570686817169189</v>
       </c>
       <c r="I36" t="n">
-        <v>7.660102844238281</v>
+        <v>8.332242965698242</v>
       </c>
       <c r="J36" t="n">
-        <v>7.483492851257324</v>
+        <v>10.38252758979797</v>
       </c>
       <c r="K36" t="n">
-        <v>8.988014221191406</v>
+        <v>10.01149606704712</v>
       </c>
       <c r="L36" t="n">
-        <v>9.347829771041869</v>
+        <v>9.637753844261169</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.969300746917725</v>
+        <v>7.946288824081421</v>
       </c>
       <c r="C37" t="n">
-        <v>6.290479421615601</v>
+        <v>6.767855882644653</v>
       </c>
       <c r="D37" t="n">
-        <v>7.312483072280884</v>
+        <v>6.339542865753174</v>
       </c>
       <c r="E37" t="n">
-        <v>6.112934112548828</v>
+        <v>6.546405792236328</v>
       </c>
       <c r="F37" t="n">
-        <v>6.295492649078369</v>
+        <v>5.882036685943604</v>
       </c>
       <c r="G37" t="n">
-        <v>6.975254535675049</v>
+        <v>6.559274196624756</v>
       </c>
       <c r="H37" t="n">
-        <v>5.602226257324219</v>
+        <v>6.747325897216797</v>
       </c>
       <c r="I37" t="n">
-        <v>6.235455274581909</v>
+        <v>6.144896507263184</v>
       </c>
       <c r="J37" t="n">
-        <v>6.714467525482178</v>
+        <v>7.246093034744263</v>
       </c>
       <c r="K37" t="n">
-        <v>6.280018091201782</v>
+        <v>6.791203737258911</v>
       </c>
       <c r="L37" t="n">
-        <v>6.378811168670654</v>
+        <v>6.697092342376709</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.492979764938354</v>
+        <v>6.858526468276978</v>
       </c>
       <c r="C38" t="n">
-        <v>7.167869806289673</v>
+        <v>7.346775054931641</v>
       </c>
       <c r="D38" t="n">
-        <v>7.631210803985596</v>
+        <v>6.737849235534668</v>
       </c>
       <c r="E38" t="n">
-        <v>9.240866184234619</v>
+        <v>6.987677335739136</v>
       </c>
       <c r="F38" t="n">
-        <v>6.684183597564697</v>
+        <v>8.740749597549438</v>
       </c>
       <c r="G38" t="n">
-        <v>6.51556658744812</v>
+        <v>6.894428968429565</v>
       </c>
       <c r="H38" t="n">
-        <v>6.270678520202637</v>
+        <v>7.941775798797607</v>
       </c>
       <c r="I38" t="n">
-        <v>6.800341129302979</v>
+        <v>7.108880281448364</v>
       </c>
       <c r="J38" t="n">
-        <v>6.456709146499634</v>
+        <v>7.520342826843262</v>
       </c>
       <c r="K38" t="n">
-        <v>7.241205453872681</v>
+        <v>6.880507946014404</v>
       </c>
       <c r="L38" t="n">
-        <v>7.050161099433899</v>
+        <v>7.301751351356506</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.102478504180908</v>
+        <v>7.504376649856567</v>
       </c>
       <c r="C39" t="n">
-        <v>6.146857023239136</v>
+        <v>7.978692054748535</v>
       </c>
       <c r="D39" t="n">
-        <v>6.360181570053101</v>
+        <v>6.711391448974609</v>
       </c>
       <c r="E39" t="n">
-        <v>6.904109716415405</v>
+        <v>6.390717267990112</v>
       </c>
       <c r="F39" t="n">
-        <v>6.304476499557495</v>
+        <v>6.668033599853516</v>
       </c>
       <c r="G39" t="n">
-        <v>6.459602355957031</v>
+        <v>6.726372957229614</v>
       </c>
       <c r="H39" t="n">
-        <v>7.061546564102173</v>
+        <v>8.177199840545654</v>
       </c>
       <c r="I39" t="n">
-        <v>6.649094581604004</v>
+        <v>7.614126443862915</v>
       </c>
       <c r="J39" t="n">
-        <v>6.304522514343262</v>
+        <v>6.591924667358398</v>
       </c>
       <c r="K39" t="n">
-        <v>6.832613945007324</v>
+        <v>8.736349105834961</v>
       </c>
       <c r="L39" t="n">
-        <v>6.512548327445984</v>
+        <v>7.309918403625488</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>6.665564775466919</v>
+        <v>9.219521999359131</v>
       </c>
       <c r="C40" t="n">
-        <v>6.757650852203369</v>
+        <v>6.993163824081421</v>
       </c>
       <c r="D40" t="n">
-        <v>7.134884357452393</v>
+        <v>7.20463752746582</v>
       </c>
       <c r="E40" t="n">
-        <v>10.01560044288635</v>
+        <v>7.74678111076355</v>
       </c>
       <c r="F40" t="n">
-        <v>7.087873458862305</v>
+        <v>7.42253041267395</v>
       </c>
       <c r="G40" t="n">
-        <v>6.629786491394043</v>
+        <v>6.81028938293457</v>
       </c>
       <c r="H40" t="n">
-        <v>6.899570941925049</v>
+        <v>7.845591306686401</v>
       </c>
       <c r="I40" t="n">
-        <v>7.156711101531982</v>
+        <v>6.670137166976929</v>
       </c>
       <c r="J40" t="n">
-        <v>6.707228422164917</v>
+        <v>7.567803382873535</v>
       </c>
       <c r="K40" t="n">
-        <v>6.787753820419312</v>
+        <v>6.731961488723755</v>
       </c>
       <c r="L40" t="n">
-        <v>7.184262466430664</v>
+        <v>7.421241760253906</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.982767105102539</v>
+        <v>7.499469041824341</v>
       </c>
       <c r="C41" t="n">
-        <v>7.770284414291382</v>
+        <v>7.887974500656128</v>
       </c>
       <c r="D41" t="n">
-        <v>8.225139856338501</v>
+        <v>10.98542165756226</v>
       </c>
       <c r="E41" t="n">
-        <v>9.931294679641724</v>
+        <v>7.580749988555908</v>
       </c>
       <c r="F41" t="n">
-        <v>7.8400719165802</v>
+        <v>7.435220956802368</v>
       </c>
       <c r="G41" t="n">
-        <v>8.64899730682373</v>
+        <v>8.487936973571777</v>
       </c>
       <c r="H41" t="n">
-        <v>7.571505784988403</v>
+        <v>11.17990517616272</v>
       </c>
       <c r="I41" t="n">
-        <v>9.897253751754761</v>
+        <v>8.763694524765015</v>
       </c>
       <c r="J41" t="n">
-        <v>8.217056035995483</v>
+        <v>11.57390880584717</v>
       </c>
       <c r="K41" t="n">
-        <v>9.196608781814575</v>
+        <v>8.383672952651978</v>
       </c>
       <c r="L41" t="n">
-        <v>8.52809796333313</v>
+        <v>8.977795457839965</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>6.33085298538208</v>
+        <v>5.846213340759277</v>
       </c>
       <c r="C42" t="n">
-        <v>6.304919958114624</v>
+        <v>9.034054279327393</v>
       </c>
       <c r="D42" t="n">
-        <v>8.881859540939331</v>
+        <v>8.233004570007324</v>
       </c>
       <c r="E42" t="n">
-        <v>6.254059553146362</v>
+        <v>6.066676139831543</v>
       </c>
       <c r="F42" t="n">
-        <v>9.46181058883667</v>
+        <v>5.303993463516235</v>
       </c>
       <c r="G42" t="n">
-        <v>6.760273456573486</v>
+        <v>10.8050000667572</v>
       </c>
       <c r="H42" t="n">
-        <v>9.206585645675659</v>
+        <v>6.495961427688599</v>
       </c>
       <c r="I42" t="n">
-        <v>5.711941957473755</v>
+        <v>6.202200889587402</v>
       </c>
       <c r="J42" t="n">
-        <v>6.048616170883179</v>
+        <v>8.424529075622559</v>
       </c>
       <c r="K42" t="n">
-        <v>8.385636806488037</v>
+        <v>6.465029001235962</v>
       </c>
       <c r="L42" t="n">
-        <v>7.334655666351319</v>
+        <v>7.28766622543335</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.946775197982788</v>
+        <v>6.037612915039062</v>
       </c>
       <c r="C43" t="n">
-        <v>8.311288833618164</v>
+        <v>7.055577516555786</v>
       </c>
       <c r="D43" t="n">
-        <v>7.144301176071167</v>
+        <v>7.955222845077515</v>
       </c>
       <c r="E43" t="n">
-        <v>6.206198930740356</v>
+        <v>7.655485868453979</v>
       </c>
       <c r="F43" t="n">
-        <v>7.195715665817261</v>
+        <v>8.771671056747437</v>
       </c>
       <c r="G43" t="n">
-        <v>7.05203104019165</v>
+        <v>6.822611808776855</v>
       </c>
       <c r="H43" t="n">
-        <v>6.813640356063843</v>
+        <v>7.126343488693237</v>
       </c>
       <c r="I43" t="n">
-        <v>6.896917581558228</v>
+        <v>6.635148048400879</v>
       </c>
       <c r="J43" t="n">
-        <v>7.096030473709106</v>
+        <v>6.886941432952881</v>
       </c>
       <c r="K43" t="n">
-        <v>7.489054918289185</v>
+        <v>8.506865262985229</v>
       </c>
       <c r="L43" t="n">
-        <v>7.215195417404175</v>
+        <v>7.345348024368286</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>8.386146783828735</v>
+        <v>8.227038621902466</v>
       </c>
       <c r="C44" t="n">
-        <v>9.904682159423828</v>
+        <v>7.600672006607056</v>
       </c>
       <c r="D44" t="n">
-        <v>7.206243276596069</v>
+        <v>8.84650182723999</v>
       </c>
       <c r="E44" t="n">
-        <v>9.785037755966187</v>
+        <v>7.212613344192505</v>
       </c>
       <c r="F44" t="n">
-        <v>9.142822504043579</v>
+        <v>8.351731538772583</v>
       </c>
       <c r="G44" t="n">
-        <v>6.665026903152466</v>
+        <v>8.426552295684814</v>
       </c>
       <c r="H44" t="n">
-        <v>7.001045942306519</v>
+        <v>6.955763578414917</v>
       </c>
       <c r="I44" t="n">
-        <v>7.649097442626953</v>
+        <v>6.912932395935059</v>
       </c>
       <c r="J44" t="n">
-        <v>9.89678168296814</v>
+        <v>6.967244863510132</v>
       </c>
       <c r="K44" t="n">
-        <v>8.152748584747314</v>
+        <v>7.049030780792236</v>
       </c>
       <c r="L44" t="n">
-        <v>8.378963303565978</v>
+        <v>7.655008125305176</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>6.842125177383423</v>
+        <v>9.806061506271362</v>
       </c>
       <c r="C45" t="n">
-        <v>9.756004095077515</v>
+        <v>10.71782064437866</v>
       </c>
       <c r="D45" t="n">
-        <v>8.727293729782104</v>
+        <v>6.985841751098633</v>
       </c>
       <c r="E45" t="n">
-        <v>6.680506706237793</v>
+        <v>8.604597330093384</v>
       </c>
       <c r="F45" t="n">
-        <v>6.671990633010864</v>
+        <v>7.609197854995728</v>
       </c>
       <c r="G45" t="n">
-        <v>7.07548999786377</v>
+        <v>8.393645524978638</v>
       </c>
       <c r="H45" t="n">
-        <v>8.63396954536438</v>
+        <v>9.605988502502441</v>
       </c>
       <c r="I45" t="n">
-        <v>6.673504114151001</v>
+        <v>11.07904195785522</v>
       </c>
       <c r="J45" t="n">
-        <v>8.800862550735474</v>
+        <v>9.275866985321045</v>
       </c>
       <c r="K45" t="n">
-        <v>9.091812372207642</v>
+        <v>10.26680564880371</v>
       </c>
       <c r="L45" t="n">
-        <v>7.895355892181397</v>
+        <v>9.234486770629882</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>8.146261215209961</v>
+        <v>7.611212015151978</v>
       </c>
       <c r="C46" t="n">
-        <v>9.381837606430054</v>
+        <v>7.812664747238159</v>
       </c>
       <c r="D46" t="n">
-        <v>7.467456817626953</v>
+        <v>8.226604461669922</v>
       </c>
       <c r="E46" t="n">
-        <v>8.026627779006958</v>
+        <v>7.088824272155762</v>
       </c>
       <c r="F46" t="n">
-        <v>8.461504459381104</v>
+        <v>7.987745761871338</v>
       </c>
       <c r="G46" t="n">
-        <v>9.122193098068237</v>
+        <v>8.323416948318481</v>
       </c>
       <c r="H46" t="n">
-        <v>6.863526105880737</v>
+        <v>7.224204301834106</v>
       </c>
       <c r="I46" t="n">
-        <v>7.248096704483032</v>
+        <v>7.407721281051636</v>
       </c>
       <c r="J46" t="n">
-        <v>6.829637765884399</v>
+        <v>7.34001350402832</v>
       </c>
       <c r="K46" t="n">
-        <v>8.067580223083496</v>
+        <v>9.620453119277954</v>
       </c>
       <c r="L46" t="n">
-        <v>7.961472177505494</v>
+        <v>7.864286041259765</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.51782751083374</v>
+        <v>8.674390316009521</v>
       </c>
       <c r="C47" t="n">
-        <v>6.81766676902771</v>
+        <v>8.318390369415283</v>
       </c>
       <c r="D47" t="n">
-        <v>8.806359529495239</v>
+        <v>9.631489753723145</v>
       </c>
       <c r="E47" t="n">
-        <v>7.494447231292725</v>
+        <v>9.668359518051147</v>
       </c>
       <c r="F47" t="n">
-        <v>6.719409942626953</v>
+        <v>8.639958143234253</v>
       </c>
       <c r="G47" t="n">
-        <v>8.868949413299561</v>
+        <v>9.151675462722778</v>
       </c>
       <c r="H47" t="n">
-        <v>6.867532968521118</v>
+        <v>9.88080906867981</v>
       </c>
       <c r="I47" t="n">
-        <v>8.219083070755005</v>
+        <v>8.68537449836731</v>
       </c>
       <c r="J47" t="n">
-        <v>8.434866905212402</v>
+        <v>7.538303375244141</v>
       </c>
       <c r="K47" t="n">
-        <v>7.379215955734253</v>
+        <v>7.98964786529541</v>
       </c>
       <c r="L47" t="n">
-        <v>7.81253592967987</v>
+        <v>8.817839837074279</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>7.957287311553955</v>
+        <v>7.47246789932251</v>
       </c>
       <c r="C48" t="n">
-        <v>6.679546117782593</v>
+        <v>6.472498178482056</v>
       </c>
       <c r="D48" t="n">
-        <v>7.673044443130493</v>
+        <v>10.59398818016052</v>
       </c>
       <c r="E48" t="n">
-        <v>8.638986110687256</v>
+        <v>6.622100114822388</v>
       </c>
       <c r="F48" t="n">
-        <v>6.549837589263916</v>
+        <v>8.632007122039795</v>
       </c>
       <c r="G48" t="n">
-        <v>6.650648593902588</v>
+        <v>6.546812534332275</v>
       </c>
       <c r="H48" t="n">
-        <v>7.508023023605347</v>
+        <v>7.0455482006073</v>
       </c>
       <c r="I48" t="n">
-        <v>6.726877927780151</v>
+        <v>7.327815771102905</v>
       </c>
       <c r="J48" t="n">
-        <v>6.472509860992432</v>
+        <v>7.886874437332153</v>
       </c>
       <c r="K48" t="n">
-        <v>7.392224311828613</v>
+        <v>6.772752046585083</v>
       </c>
       <c r="L48" t="n">
-        <v>7.224898529052735</v>
+        <v>7.537286448478699</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.190721750259399</v>
+        <v>7.968733072280884</v>
       </c>
       <c r="C49" t="n">
-        <v>7.575745820999146</v>
+        <v>9.644420385360718</v>
       </c>
       <c r="D49" t="n">
-        <v>6.996700286865234</v>
+        <v>7.636307239532471</v>
       </c>
       <c r="E49" t="n">
-        <v>7.509374856948853</v>
+        <v>8.599642038345337</v>
       </c>
       <c r="F49" t="n">
-        <v>7.531371116638184</v>
+        <v>7.671547889709473</v>
       </c>
       <c r="G49" t="n">
-        <v>6.834113359451294</v>
+        <v>8.015144824981689</v>
       </c>
       <c r="H49" t="n">
-        <v>9.511858463287354</v>
+        <v>7.604247808456421</v>
       </c>
       <c r="I49" t="n">
-        <v>9.065619230270386</v>
+        <v>8.218384742736816</v>
       </c>
       <c r="J49" t="n">
-        <v>8.337569713592529</v>
+        <v>7.640503406524658</v>
       </c>
       <c r="K49" t="n">
-        <v>8.407238245010376</v>
+        <v>7.964210271835327</v>
       </c>
       <c r="L49" t="n">
-        <v>7.896031284332276</v>
+        <v>8.096314167976379</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>9.359230518341064</v>
+        <v>9.153711795806885</v>
       </c>
       <c r="C50" t="n">
-        <v>9.488005638122559</v>
+        <v>8.693867444992065</v>
       </c>
       <c r="D50" t="n">
-        <v>7.672017335891724</v>
+        <v>7.678447484970093</v>
       </c>
       <c r="E50" t="n">
-        <v>6.734388589859009</v>
+        <v>7.166738748550415</v>
       </c>
       <c r="F50" t="n">
-        <v>10.28983759880066</v>
+        <v>8.057457447052002</v>
       </c>
       <c r="G50" t="n">
-        <v>6.99418044090271</v>
+        <v>7.789182186126709</v>
       </c>
       <c r="H50" t="n">
-        <v>7.241595983505249</v>
+        <v>10.78598475456238</v>
       </c>
       <c r="I50" t="n">
-        <v>8.818341493606567</v>
+        <v>8.328293085098267</v>
       </c>
       <c r="J50" t="n">
-        <v>7.002173900604248</v>
+        <v>7.767271757125854</v>
       </c>
       <c r="K50" t="n">
-        <v>7.911379814147949</v>
+        <v>7.963220119476318</v>
       </c>
       <c r="L50" t="n">
-        <v>8.151115131378173</v>
+        <v>8.338417482376098</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.200596332550049</v>
+        <v>7.52934718132019</v>
       </c>
       <c r="C51" t="n">
-        <v>7.562832355499268</v>
+        <v>7.440041065216064</v>
       </c>
       <c r="D51" t="n">
-        <v>8.322424173355103</v>
+        <v>8.148777961730957</v>
       </c>
       <c r="E51" t="n">
-        <v>7.915572643280029</v>
+        <v>7.15776252746582</v>
       </c>
       <c r="F51" t="n">
-        <v>7.601174831390381</v>
+        <v>7.616578817367554</v>
       </c>
       <c r="G51" t="n">
-        <v>7.135870456695557</v>
+        <v>7.455028533935547</v>
       </c>
       <c r="H51" t="n">
-        <v>6.591302633285522</v>
+        <v>8.020561695098877</v>
       </c>
       <c r="I51" t="n">
-        <v>8.015237331390381</v>
+        <v>7.407136678695679</v>
       </c>
       <c r="J51" t="n">
-        <v>6.946385860443115</v>
+        <v>8.491860866546631</v>
       </c>
       <c r="K51" t="n">
-        <v>8.103357315063477</v>
+        <v>7.752750873565674</v>
       </c>
       <c r="L51" t="n">
-        <v>7.539475393295288</v>
+        <v>7.701984620094299</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.723084201812744</v>
+        <v>8.03445191860199</v>
       </c>
       <c r="C52" t="n">
-        <v>7.632897725105286</v>
+        <v>8.190669045448303</v>
       </c>
       <c r="D52" t="n">
-        <v>7.622943153381348</v>
+        <v>8.107958970069886</v>
       </c>
       <c r="E52" t="n">
-        <v>7.741663041114808</v>
+        <v>7.884214744567871</v>
       </c>
       <c r="F52" t="n">
-        <v>7.8262668800354</v>
+        <v>7.959370059967041</v>
       </c>
       <c r="G52" t="n">
-        <v>7.608863043785095</v>
+        <v>7.960185613632202</v>
       </c>
       <c r="H52" t="n">
-        <v>7.566508965492249</v>
+        <v>8.118857793807983</v>
       </c>
       <c r="I52" t="n">
-        <v>7.476014752388</v>
+        <v>8.048329076766969</v>
       </c>
       <c r="J52" t="n">
-        <v>7.796268067359924</v>
+        <v>7.914394598007203</v>
       </c>
       <c r="K52" t="n">
-        <v>7.709697155952454</v>
+        <v>8.737937531471253</v>
       </c>
       <c r="L52" t="n">
-        <v>7.670420698642731</v>
+        <v>8.09563693523407</v>
       </c>
     </row>
   </sheetData>
